--- a/research/traditional_assets/database/data/peru/peru_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_chemical_basic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1043279414132504</v>
+        <v>0.1040518989860813</v>
       </c>
       <c r="C2">
-        <v>323.8810667514879</v>
+        <v>321.5230639713489</v>
       </c>
       <c r="D2">
-        <v>290.5810667514879</v>
+        <v>291.9580639713489</v>
       </c>
       <c r="E2">
-        <v>-285.8</v>
+        <v>-282.065</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.735</v>
       </c>
       <c r="G2">
         <v>33.3</v>
@@ -1451,28 +1451,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1878705</v>
       </c>
       <c r="N2">
-        <v>74.72499999999999</v>
+        <v>74.53712949999999</v>
       </c>
       <c r="O2">
-        <v>22.043875</v>
+        <v>21.9884532025</v>
       </c>
       <c r="P2">
-        <v>52.68112499999999</v>
+        <v>52.54867629749999</v>
       </c>
       <c r="Q2">
-        <v>84.58112499999999</v>
+        <v>84.44867629749999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1043279414132504</v>
+        <v>0.104744731299072</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470866</v>
+        <v>0.9118562465256794</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>397.7473845015582</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1040518989860813</v>
+        <v>0.1037758565589122</v>
       </c>
       <c r="C3">
-        <v>321.5230639713489</v>
+        <v>319.1781738790541</v>
       </c>
       <c r="D3">
-        <v>291.9580639713489</v>
+        <v>293.3481738790541</v>
       </c>
       <c r="E3">
-        <v>-282.065</v>
+        <v>-278.33</v>
       </c>
       <c r="F3">
-        <v>3.735</v>
+        <v>7.47</v>
       </c>
       <c r="G3">
         <v>33.3</v>
@@ -1533,28 +1533,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M3">
-        <v>0.1878705</v>
+        <v>0.375741</v>
       </c>
       <c r="N3">
-        <v>74.53712949999999</v>
+        <v>74.34925899999999</v>
       </c>
       <c r="O3">
-        <v>21.9884532025</v>
+        <v>21.93303140499999</v>
       </c>
       <c r="P3">
-        <v>52.54867629749999</v>
+        <v>52.416227595</v>
       </c>
       <c r="Q3">
-        <v>84.44867629749999</v>
+        <v>84.31622759499999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.104744731299072</v>
+        <v>0.1051700271009308</v>
       </c>
       <c r="T3">
-        <v>0.9118562465256794</v>
+        <v>0.9184354373201621</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>397.7473845015582</v>
+        <v>198.8736922507791</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1037758565589122</v>
+        <v>0.1034998141317431</v>
       </c>
       <c r="C4">
-        <v>319.1781738790541</v>
+        <v>316.8465846723421</v>
       </c>
       <c r="D4">
-        <v>293.3481738790541</v>
+        <v>294.7515846723421</v>
       </c>
       <c r="E4">
-        <v>-278.33</v>
+        <v>-274.595</v>
       </c>
       <c r="F4">
-        <v>7.47</v>
+        <v>11.205</v>
       </c>
       <c r="G4">
         <v>33.3</v>
@@ -1615,28 +1615,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M4">
-        <v>0.375741</v>
+        <v>0.5636114999999999</v>
       </c>
       <c r="N4">
-        <v>74.34925899999999</v>
+        <v>74.1613885</v>
       </c>
       <c r="O4">
-        <v>21.93303140499999</v>
+        <v>21.8776096075</v>
       </c>
       <c r="P4">
-        <v>52.416227595</v>
+        <v>52.2837788925</v>
       </c>
       <c r="Q4">
-        <v>84.31622759499999</v>
+        <v>84.1837788925</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1051700271009308</v>
+        <v>0.105604091888395</v>
       </c>
       <c r="T4">
-        <v>0.9184354373201621</v>
+        <v>0.9251502815330875</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>198.8736922507791</v>
+        <v>132.5824615005194</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1034998141317431</v>
+        <v>0.103223771704574</v>
       </c>
       <c r="C5">
-        <v>316.8465846723421</v>
+        <v>314.5284881677007</v>
       </c>
       <c r="D5">
-        <v>294.7515846723421</v>
+        <v>296.1684881677007</v>
       </c>
       <c r="E5">
-        <v>-274.595</v>
+        <v>-270.86</v>
       </c>
       <c r="F5">
-        <v>11.205</v>
+        <v>14.94</v>
       </c>
       <c r="G5">
         <v>33.3</v>
@@ -1697,28 +1697,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M5">
-        <v>0.5636114999999999</v>
+        <v>0.751482</v>
       </c>
       <c r="N5">
-        <v>74.1613885</v>
+        <v>73.973518</v>
       </c>
       <c r="O5">
-        <v>21.8776096075</v>
+        <v>21.82218781</v>
       </c>
       <c r="P5">
-        <v>52.2837788925</v>
+        <v>52.15133019</v>
       </c>
       <c r="Q5">
-        <v>84.1837788925</v>
+        <v>84.05133018999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.105604091888395</v>
+        <v>0.1060471996922646</v>
       </c>
       <c r="T5">
-        <v>0.9251502815330875</v>
+        <v>0.9320050183337822</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>132.5824615005194</v>
+        <v>99.43684612538956</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.103223771704574</v>
+        <v>0.1029477292774049</v>
       </c>
       <c r="C6">
-        <v>314.5284881677007</v>
+        <v>312.2240798877665</v>
       </c>
       <c r="D6">
-        <v>296.1684881677007</v>
+        <v>297.5990798877665</v>
       </c>
       <c r="E6">
-        <v>-270.86</v>
+        <v>-267.125</v>
       </c>
       <c r="F6">
-        <v>14.94</v>
+        <v>18.675</v>
       </c>
       <c r="G6">
         <v>33.3</v>
@@ -1779,28 +1779,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M6">
-        <v>0.751482</v>
+        <v>0.9393525</v>
       </c>
       <c r="N6">
-        <v>73.973518</v>
+        <v>73.7856475</v>
       </c>
       <c r="O6">
-        <v>21.82218781</v>
+        <v>21.7667660125</v>
       </c>
       <c r="P6">
-        <v>52.15133019</v>
+        <v>52.0188814875</v>
       </c>
       <c r="Q6">
-        <v>84.05133018999999</v>
+        <v>83.91888148749999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1060471996922646</v>
+        <v>0.1064996360814789</v>
       </c>
       <c r="T6">
-        <v>0.9320050183337822</v>
+        <v>0.9390040653829127</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>99.43684612538956</v>
+        <v>79.54947690031165</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1029477292774049</v>
+        <v>0.1026716868502358</v>
       </c>
       <c r="C7">
-        <v>312.2240798877665</v>
+        <v>309.9335591512677</v>
       </c>
       <c r="D7">
-        <v>297.5990798877665</v>
+        <v>299.0435591512677</v>
       </c>
       <c r="E7">
-        <v>-267.125</v>
+        <v>-263.39</v>
       </c>
       <c r="F7">
-        <v>18.675</v>
+        <v>22.41</v>
       </c>
       <c r="G7">
         <v>33.3</v>
@@ -1861,28 +1861,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M7">
-        <v>0.9393525</v>
+        <v>1.127223</v>
       </c>
       <c r="N7">
-        <v>73.7856475</v>
+        <v>73.59777699999999</v>
       </c>
       <c r="O7">
-        <v>21.7667660125</v>
+        <v>21.711344215</v>
       </c>
       <c r="P7">
-        <v>52.0188814875</v>
+        <v>51.886432785</v>
       </c>
       <c r="Q7">
-        <v>83.91888148749999</v>
+        <v>83.78643278499999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1064996360814789</v>
+        <v>0.1069616987768466</v>
       </c>
       <c r="T7">
-        <v>0.9390040653829127</v>
+        <v>0.9461520283267054</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>79.54947690031165</v>
+        <v>66.29123075025971</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1026716868502358</v>
+        <v>0.1023956444230668</v>
       </c>
       <c r="C8">
-        <v>309.9335591512677</v>
+        <v>307.6571291656017</v>
       </c>
       <c r="D8">
-        <v>299.0435591512677</v>
+        <v>300.5021291656017</v>
       </c>
       <c r="E8">
-        <v>-263.39</v>
+        <v>-259.655</v>
       </c>
       <c r="F8">
-        <v>22.41</v>
+        <v>26.145</v>
       </c>
       <c r="G8">
         <v>33.3</v>
@@ -1943,28 +1943,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M8">
-        <v>1.127223</v>
+        <v>1.3150935</v>
       </c>
       <c r="N8">
-        <v>73.59777699999999</v>
+        <v>73.40990649999999</v>
       </c>
       <c r="O8">
-        <v>21.711344215</v>
+        <v>21.6559224175</v>
       </c>
       <c r="P8">
-        <v>51.886432785</v>
+        <v>51.7539840825</v>
       </c>
       <c r="Q8">
-        <v>83.78643278499999</v>
+        <v>83.65398408249999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1069616987768466</v>
+        <v>0.1074336983043729</v>
       </c>
       <c r="T8">
-        <v>0.9461520283267054</v>
+        <v>0.9534537109036981</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>66.29123075025971</v>
+        <v>56.82105492879404</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1023956444230668</v>
+        <v>0.1021196019958977</v>
       </c>
       <c r="C9">
-        <v>307.6571291656018</v>
+        <v>305.394997122133</v>
       </c>
       <c r="D9">
-        <v>300.5021291656017</v>
+        <v>301.9749971221329</v>
       </c>
       <c r="E9">
-        <v>-259.655</v>
+        <v>-255.92</v>
       </c>
       <c r="F9">
-        <v>26.145</v>
+        <v>29.88</v>
       </c>
       <c r="G9">
         <v>33.3</v>
@@ -2025,28 +2025,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M9">
-        <v>1.3150935</v>
+        <v>1.502964</v>
       </c>
       <c r="N9">
-        <v>73.40990649999999</v>
+        <v>73.22203599999999</v>
       </c>
       <c r="O9">
-        <v>21.6559224175</v>
+        <v>21.60050061999999</v>
       </c>
       <c r="P9">
-        <v>51.7539840825</v>
+        <v>51.62153538</v>
       </c>
       <c r="Q9">
-        <v>83.65398408249999</v>
+        <v>83.52153537999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1074336983043729</v>
+        <v>0.1079159586911931</v>
       </c>
       <c r="T9">
-        <v>0.9534537109036981</v>
+        <v>0.9609141257106253</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>56.82105492879403</v>
+        <v>49.71842306269478</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1021196019958977</v>
+        <v>0.1018435595687286</v>
       </c>
       <c r="C10">
-        <v>305.394997122133</v>
+        <v>303.1473742943083</v>
       </c>
       <c r="D10">
-        <v>301.9749971221329</v>
+        <v>303.4623742943083</v>
       </c>
       <c r="E10">
-        <v>-255.92</v>
+        <v>-252.185</v>
       </c>
       <c r="F10">
-        <v>29.88</v>
+        <v>33.615</v>
       </c>
       <c r="G10">
         <v>33.3</v>
@@ -2107,28 +2107,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M10">
-        <v>1.502964</v>
+        <v>1.6908345</v>
       </c>
       <c r="N10">
-        <v>73.22203599999999</v>
+        <v>73.0341655</v>
       </c>
       <c r="O10">
-        <v>21.60050061999999</v>
+        <v>21.5450788225</v>
       </c>
       <c r="P10">
-        <v>51.62153538</v>
+        <v>51.4890866775</v>
       </c>
       <c r="Q10">
-        <v>83.52153537999999</v>
+        <v>83.38908667749999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1079159586911931</v>
+        <v>0.108408818207394</v>
       </c>
       <c r="T10">
-        <v>0.9609141257106253</v>
+        <v>0.9685385056781445</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>49.71842306269478</v>
+        <v>44.19415383350647</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1018435595687286</v>
+        <v>0.1015675171415595</v>
       </c>
       <c r="C11">
-        <v>303.1473742943083</v>
+        <v>300.9144761386859</v>
       </c>
       <c r="D11">
-        <v>303.4623742943083</v>
+        <v>304.9644761386859</v>
       </c>
       <c r="E11">
-        <v>-252.185</v>
+        <v>-248.45</v>
       </c>
       <c r="F11">
-        <v>33.615</v>
+        <v>37.34999999999999</v>
       </c>
       <c r="G11">
         <v>33.3</v>
@@ -2189,28 +2189,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M11">
-        <v>1.6908345</v>
+        <v>1.878705</v>
       </c>
       <c r="N11">
-        <v>73.0341655</v>
+        <v>72.846295</v>
       </c>
       <c r="O11">
-        <v>21.5450788225</v>
+        <v>21.489657025</v>
       </c>
       <c r="P11">
-        <v>51.4890866775</v>
+        <v>51.356637975</v>
       </c>
       <c r="Q11">
-        <v>83.38908667749999</v>
+        <v>83.25663797499999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.108408818207394</v>
+        <v>0.1089126301572883</v>
       </c>
       <c r="T11">
-        <v>0.9685385056781445</v>
+        <v>0.9763323163116084</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>44.19415383350647</v>
+        <v>39.77473845015583</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1015675171415595</v>
+        <v>0.1012914747143904</v>
       </c>
       <c r="C12">
-        <v>300.9144761386859</v>
+        <v>298.69652239898</v>
       </c>
       <c r="D12">
-        <v>304.9644761386859</v>
+        <v>306.48152239898</v>
       </c>
       <c r="E12">
-        <v>-248.45</v>
+        <v>-244.715</v>
       </c>
       <c r="F12">
-        <v>37.35</v>
+        <v>41.085</v>
       </c>
       <c r="G12">
         <v>33.3</v>
@@ -2271,28 +2271,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M12">
-        <v>1.878705</v>
+        <v>2.0665755</v>
       </c>
       <c r="N12">
-        <v>72.846295</v>
+        <v>72.6584245</v>
       </c>
       <c r="O12">
-        <v>21.489657025</v>
+        <v>21.4342352275</v>
       </c>
       <c r="P12">
-        <v>51.356637975</v>
+        <v>51.2241892725</v>
       </c>
       <c r="Q12">
-        <v>83.25663797499999</v>
+        <v>83.12418927249999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1089126301572883</v>
+        <v>0.1094277637240341</v>
       </c>
       <c r="T12">
-        <v>0.9763323163116084</v>
+        <v>0.9843012687570603</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>39.77473845015582</v>
+        <v>36.15885313650529</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1012914747143904</v>
+        <v>0.1010154322872213</v>
       </c>
       <c r="C13">
-        <v>298.69652239898</v>
+        <v>296.4937372132263</v>
       </c>
       <c r="D13">
-        <v>306.48152239898</v>
+        <v>308.0137372132263</v>
       </c>
       <c r="E13">
-        <v>-244.715</v>
+        <v>-240.98</v>
       </c>
       <c r="F13">
-        <v>41.085</v>
+        <v>44.82</v>
       </c>
       <c r="G13">
         <v>33.3</v>
@@ -2353,28 +2353,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M13">
-        <v>2.0665755</v>
+        <v>2.254446</v>
       </c>
       <c r="N13">
-        <v>72.6584245</v>
+        <v>72.47055399999999</v>
       </c>
       <c r="O13">
-        <v>21.4342352275</v>
+        <v>21.37881343</v>
       </c>
       <c r="P13">
-        <v>51.2241892725</v>
+        <v>51.09174057</v>
       </c>
       <c r="Q13">
-        <v>83.12418927249999</v>
+        <v>82.99174056999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1094277637240341</v>
+        <v>0.1099546048718424</v>
       </c>
       <c r="T13">
-        <v>0.9843012687570603</v>
+        <v>0.9924513337580907</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>36.15885313650529</v>
+        <v>33.14561537512986</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1010154322872213</v>
+        <v>0.1007393898600522</v>
       </c>
       <c r="C14">
-        <v>296.4937372132263</v>
+        <v>294.3063492241776</v>
       </c>
       <c r="D14">
-        <v>308.0137372132263</v>
+        <v>309.5613492241776</v>
       </c>
       <c r="E14">
-        <v>-240.98</v>
+        <v>-237.245</v>
       </c>
       <c r="F14">
-        <v>44.82</v>
+        <v>48.555</v>
       </c>
       <c r="G14">
         <v>33.3</v>
@@ -2435,28 +2435,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M14">
-        <v>2.254446</v>
+        <v>2.4423165</v>
       </c>
       <c r="N14">
-        <v>72.47055399999999</v>
+        <v>72.28268349999999</v>
       </c>
       <c r="O14">
-        <v>21.37881343</v>
+        <v>21.32339163249999</v>
       </c>
       <c r="P14">
-        <v>51.09174057</v>
+        <v>50.9592918675</v>
       </c>
       <c r="Q14">
-        <v>82.99174056999999</v>
+        <v>82.85929186749999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1099546048718424</v>
+        <v>0.1104935573104049</v>
       </c>
       <c r="T14">
-        <v>0.9924513337580907</v>
+        <v>1.000788756575237</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>33.14561537512986</v>
+        <v>30.59595265396602</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1007393898600522</v>
+        <v>0.1004633474328831</v>
       </c>
       <c r="C15">
-        <v>294.3063492241776</v>
+        <v>292.1345916930459</v>
       </c>
       <c r="D15">
-        <v>309.5613492241776</v>
+        <v>311.1245916930459</v>
       </c>
       <c r="E15">
-        <v>-237.245</v>
+        <v>-233.51</v>
       </c>
       <c r="F15">
-        <v>48.555</v>
+        <v>52.29000000000001</v>
       </c>
       <c r="G15">
         <v>33.3</v>
@@ -2517,28 +2517,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M15">
-        <v>2.4423165</v>
+        <v>2.630187</v>
       </c>
       <c r="N15">
-        <v>72.28268349999999</v>
+        <v>72.09481299999999</v>
       </c>
       <c r="O15">
-        <v>21.32339163249999</v>
+        <v>21.267969835</v>
       </c>
       <c r="P15">
-        <v>50.9592918675</v>
+        <v>50.82684316499999</v>
       </c>
       <c r="Q15">
-        <v>82.85929186749999</v>
+        <v>82.72684316499999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1104935573104049</v>
+        <v>0.1110450435266083</v>
       </c>
       <c r="T15">
-        <v>1.000788756575237</v>
+        <v>1.00932007294627</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.59595265396602</v>
+        <v>28.41052746439701</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1004633474328831</v>
+        <v>0.100187305005714</v>
       </c>
       <c r="C16">
-        <v>292.1345916930459</v>
+        <v>289.9787026167057</v>
       </c>
       <c r="D16">
-        <v>311.1245916930459</v>
+        <v>312.7037026167058</v>
       </c>
       <c r="E16">
-        <v>-233.51</v>
+        <v>-229.775</v>
       </c>
       <c r="F16">
-        <v>52.29000000000001</v>
+        <v>56.02500000000001</v>
       </c>
       <c r="G16">
         <v>33.3</v>
@@ -2599,28 +2599,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M16">
-        <v>2.630187</v>
+        <v>2.8180575</v>
       </c>
       <c r="N16">
-        <v>72.09481299999999</v>
+        <v>71.9069425</v>
       </c>
       <c r="O16">
-        <v>21.267969835</v>
+        <v>21.2125480375</v>
       </c>
       <c r="P16">
-        <v>50.82684316499999</v>
+        <v>50.6943944625</v>
       </c>
       <c r="Q16">
-        <v>82.72684316499999</v>
+        <v>82.59439446249999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1110450435266083</v>
+        <v>0.1116095058890753</v>
       </c>
       <c r="T16">
-        <v>1.00932007294627</v>
+        <v>1.018052126173092</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.41052746439701</v>
+        <v>26.51649230010388</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.100187305005714</v>
+        <v>0.09991126257854495</v>
       </c>
       <c r="C17">
-        <v>289.9787026167058</v>
+        <v>287.8389248484875</v>
       </c>
       <c r="D17">
-        <v>312.7037026167058</v>
+        <v>314.2989248484875</v>
       </c>
       <c r="E17">
-        <v>-229.775</v>
+        <v>-226.04</v>
       </c>
       <c r="F17">
-        <v>56.025</v>
+        <v>59.76</v>
       </c>
       <c r="G17">
         <v>33.3</v>
@@ -2681,28 +2681,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M17">
-        <v>2.8180575</v>
+        <v>3.005928</v>
       </c>
       <c r="N17">
-        <v>71.9069425</v>
+        <v>71.719072</v>
       </c>
       <c r="O17">
-        <v>21.2125480375</v>
+        <v>21.15712624</v>
       </c>
       <c r="P17">
-        <v>50.6943944625</v>
+        <v>50.56194576</v>
       </c>
       <c r="Q17">
-        <v>82.59439446249999</v>
+        <v>82.46194575999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1116095058890753</v>
+        <v>0.1121874078316011</v>
       </c>
       <c r="T17">
-        <v>1.018052126173092</v>
+        <v>1.026992085429124</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.51649230010389</v>
+        <v>24.85921153134739</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09991126257854495</v>
+        <v>0.09963522015137585</v>
       </c>
       <c r="C18">
-        <v>287.8389248484875</v>
+        <v>285.7155062226856</v>
       </c>
       <c r="D18">
-        <v>314.2989248484875</v>
+        <v>315.9105062226856</v>
       </c>
       <c r="E18">
-        <v>-226.04</v>
+        <v>-222.305</v>
       </c>
       <c r="F18">
-        <v>59.76</v>
+        <v>63.495</v>
       </c>
       <c r="G18">
         <v>33.3</v>
@@ -2763,28 +2763,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M18">
-        <v>3.005928</v>
+        <v>3.1937985</v>
       </c>
       <c r="N18">
-        <v>71.719072</v>
+        <v>71.53120149999999</v>
       </c>
       <c r="O18">
-        <v>21.15712624</v>
+        <v>21.1017044425</v>
       </c>
       <c r="P18">
-        <v>50.56194576</v>
+        <v>50.4294970575</v>
       </c>
       <c r="Q18">
-        <v>82.46194575999999</v>
+        <v>82.32949705749999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1121874078316011</v>
+        <v>0.1127792351221396</v>
       </c>
       <c r="T18">
-        <v>1.026992085429124</v>
+        <v>1.036147465390121</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.85921153134739</v>
+        <v>23.39690497067989</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09963522015137585</v>
+        <v>0.09935917772420676</v>
       </c>
       <c r="C19">
-        <v>285.7155062226856</v>
+        <v>283.6086996829171</v>
       </c>
       <c r="D19">
-        <v>315.9105062226856</v>
+        <v>317.5386996829171</v>
       </c>
       <c r="E19">
-        <v>-222.305</v>
+        <v>-218.57</v>
       </c>
       <c r="F19">
-        <v>63.495</v>
+        <v>67.23</v>
       </c>
       <c r="G19">
         <v>33.3</v>
@@ -2845,28 +2845,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M19">
-        <v>3.1937985</v>
+        <v>3.381669</v>
       </c>
       <c r="N19">
-        <v>71.53120149999999</v>
+        <v>71.34333099999999</v>
       </c>
       <c r="O19">
-        <v>21.1017044425</v>
+        <v>21.046282645</v>
       </c>
       <c r="P19">
-        <v>50.4294970575</v>
+        <v>50.29704835499999</v>
       </c>
       <c r="Q19">
-        <v>82.32949705749999</v>
+        <v>82.19704835499999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1127792351221396</v>
+        <v>0.1133854972246424</v>
       </c>
       <c r="T19">
-        <v>1.036147465390121</v>
+        <v>1.045526147301386</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.39690497067989</v>
+        <v>22.09707691675323</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09935917772420677</v>
+        <v>0.09908313529703769</v>
       </c>
       <c r="C20">
-        <v>283.608699682917</v>
+        <v>281.51876341447</v>
       </c>
       <c r="D20">
-        <v>317.538699682917</v>
+        <v>319.18376341447</v>
       </c>
       <c r="E20">
-        <v>-218.57</v>
+        <v>-214.835</v>
       </c>
       <c r="F20">
-        <v>67.23</v>
+        <v>70.965</v>
       </c>
       <c r="G20">
         <v>33.3</v>
@@ -2927,28 +2927,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M20">
-        <v>3.381669</v>
+        <v>3.5695395</v>
       </c>
       <c r="N20">
-        <v>71.34333099999999</v>
+        <v>71.15546049999999</v>
       </c>
       <c r="O20">
-        <v>21.046282645</v>
+        <v>20.9908608475</v>
       </c>
       <c r="P20">
-        <v>50.29704835499999</v>
+        <v>50.16459965249999</v>
       </c>
       <c r="Q20">
-        <v>82.19704835499999</v>
+        <v>82.06459965249999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1133854972246424</v>
+        <v>0.1140067287617749</v>
       </c>
       <c r="T20">
-        <v>1.045526147301386</v>
+        <v>1.055136401605522</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.09707691675323</v>
+        <v>20.93407286850307</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09908313529703769</v>
+        <v>0.09880709286986859</v>
       </c>
       <c r="C21">
-        <v>281.51876341447</v>
+        <v>279.4459609807882</v>
       </c>
       <c r="D21">
-        <v>319.18376341447</v>
+        <v>320.8459609807882</v>
       </c>
       <c r="E21">
-        <v>-214.835</v>
+        <v>-211.1</v>
       </c>
       <c r="F21">
-        <v>70.965</v>
+        <v>74.7</v>
       </c>
       <c r="G21">
         <v>33.3</v>
@@ -3009,28 +3009,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M21">
-        <v>3.5695395</v>
+        <v>3.75741</v>
       </c>
       <c r="N21">
-        <v>71.15546049999999</v>
+        <v>70.96759</v>
       </c>
       <c r="O21">
-        <v>20.9908608475</v>
+        <v>20.93543905</v>
       </c>
       <c r="P21">
-        <v>50.16459965249999</v>
+        <v>50.03215095</v>
       </c>
       <c r="Q21">
-        <v>82.06459965249999</v>
+        <v>81.93215094999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1140067287617749</v>
+        <v>0.1146434910873357</v>
       </c>
       <c r="T21">
-        <v>1.055136401605522</v>
+        <v>1.064986912267261</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.93407286850307</v>
+        <v>19.88736922507791</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09880709286986859</v>
+        <v>0.09853105044269951</v>
       </c>
       <c r="C22">
-        <v>279.4459609807882</v>
+        <v>277.390561464241</v>
       </c>
       <c r="D22">
-        <v>320.8459609807882</v>
+        <v>322.525561464241</v>
       </c>
       <c r="E22">
-        <v>-211.1</v>
+        <v>-207.365</v>
       </c>
       <c r="F22">
-        <v>74.7</v>
+        <v>78.435</v>
       </c>
       <c r="G22">
         <v>33.3</v>
@@ -3091,28 +3091,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M22">
-        <v>3.75741</v>
+        <v>3.9452805</v>
       </c>
       <c r="N22">
-        <v>70.96759</v>
+        <v>70.7797195</v>
       </c>
       <c r="O22">
-        <v>20.93543905</v>
+        <v>20.8800172525</v>
       </c>
       <c r="P22">
-        <v>50.03215095</v>
+        <v>49.8997022475</v>
       </c>
       <c r="Q22">
-        <v>81.93215094999999</v>
+        <v>81.79970224749999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1146434910873357</v>
+        <v>0.1152963739781006</v>
       </c>
       <c r="T22">
-        <v>1.064986912267261</v>
+        <v>1.075086802945753</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.88736922507791</v>
+        <v>18.94035164293135</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09853105044269951</v>
+        <v>0.09825500801553043</v>
       </c>
       <c r="C23">
-        <v>277.390561464241</v>
+        <v>275.35283961134</v>
       </c>
       <c r="D23">
-        <v>322.525561464241</v>
+        <v>324.22283961134</v>
       </c>
       <c r="E23">
-        <v>-207.365</v>
+        <v>-203.63</v>
       </c>
       <c r="F23">
-        <v>78.435</v>
+        <v>82.17</v>
       </c>
       <c r="G23">
         <v>33.3</v>
@@ -3173,28 +3173,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M23">
-        <v>3.9452805</v>
+        <v>4.133151</v>
       </c>
       <c r="N23">
-        <v>70.7797195</v>
+        <v>70.591849</v>
       </c>
       <c r="O23">
-        <v>20.8800172525</v>
+        <v>20.824595455</v>
       </c>
       <c r="P23">
-        <v>49.8997022475</v>
+        <v>49.767253545</v>
       </c>
       <c r="Q23">
-        <v>81.79970224749999</v>
+        <v>81.66725354499999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1152963739781006</v>
+        <v>0.1159659974558082</v>
       </c>
       <c r="T23">
-        <v>1.075086802945753</v>
+        <v>1.085445665180103</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.94035164293135</v>
+        <v>18.07942656825265</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09825500801553043</v>
+        <v>0.09797896558836133</v>
       </c>
       <c r="C24">
-        <v>275.35283961134</v>
+        <v>273.3330759825633</v>
       </c>
       <c r="D24">
-        <v>324.22283961134</v>
+        <v>325.9380759825633</v>
       </c>
       <c r="E24">
-        <v>-203.63</v>
+        <v>-199.895</v>
       </c>
       <c r="F24">
-        <v>82.17</v>
+        <v>85.905</v>
       </c>
       <c r="G24">
         <v>33.3</v>
@@ -3255,28 +3255,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M24">
-        <v>4.133151</v>
+        <v>4.3210215</v>
       </c>
       <c r="N24">
-        <v>70.591849</v>
+        <v>70.40397849999999</v>
       </c>
       <c r="O24">
-        <v>20.824595455</v>
+        <v>20.7691736575</v>
       </c>
       <c r="P24">
-        <v>49.767253545</v>
+        <v>49.6348048425</v>
       </c>
       <c r="Q24">
-        <v>81.66725354499999</v>
+        <v>81.53480484249999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1159659974558082</v>
+        <v>0.1166530137511186</v>
       </c>
       <c r="T24">
-        <v>1.085445665180103</v>
+        <v>1.096073588771191</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.07942656825265</v>
+        <v>17.29336454354601</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09797896558836133</v>
+        <v>0.09770292316119225</v>
       </c>
       <c r="C25">
-        <v>273.3330759825633</v>
+        <v>271.3315571069621</v>
       </c>
       <c r="D25">
-        <v>325.9380759825633</v>
+        <v>327.6715571069621</v>
       </c>
       <c r="E25">
-        <v>-199.895</v>
+        <v>-196.16</v>
       </c>
       <c r="F25">
-        <v>85.905</v>
+        <v>89.64</v>
       </c>
       <c r="G25">
         <v>33.3</v>
@@ -3337,28 +3337,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M25">
-        <v>4.3210215</v>
+        <v>4.508891999999999</v>
       </c>
       <c r="N25">
-        <v>70.40397849999999</v>
+        <v>70.21610799999999</v>
       </c>
       <c r="O25">
-        <v>20.7691736575</v>
+        <v>20.71375186</v>
       </c>
       <c r="P25">
-        <v>49.6348048425</v>
+        <v>49.50235614</v>
       </c>
       <c r="Q25">
-        <v>81.53480484249999</v>
+        <v>81.40235613999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1166530137511186</v>
+        <v>0.1173581094226214</v>
       </c>
       <c r="T25">
-        <v>1.096073588771191</v>
+        <v>1.106981194562043</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.29336454354601</v>
+        <v>16.57280768756493</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09770292316119225</v>
+        <v>0.09742688073402316</v>
       </c>
       <c r="C26">
-        <v>271.3315571069621</v>
+        <v>269.3485756417265</v>
       </c>
       <c r="D26">
-        <v>327.6715571069621</v>
+        <v>329.4235756417265</v>
       </c>
       <c r="E26">
-        <v>-196.16</v>
+        <v>-192.425</v>
       </c>
       <c r="F26">
-        <v>89.64</v>
+        <v>93.375</v>
       </c>
       <c r="G26">
         <v>33.3</v>
@@ -3419,28 +3419,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M26">
-        <v>4.508891999999999</v>
+        <v>4.6967625</v>
       </c>
       <c r="N26">
-        <v>70.21610799999999</v>
+        <v>70.02823749999999</v>
       </c>
       <c r="O26">
-        <v>20.71375186</v>
+        <v>20.6583300625</v>
       </c>
       <c r="P26">
-        <v>49.50235614</v>
+        <v>49.36990743749999</v>
       </c>
       <c r="Q26">
-        <v>81.40235613999999</v>
+        <v>81.2699074375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1173581094226214</v>
+        <v>0.1180820076453642</v>
       </c>
       <c r="T26">
-        <v>1.106981194562043</v>
+        <v>1.118179669840652</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.57280768756493</v>
+        <v>15.90989538006233</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09742688073402316</v>
+        <v>0.09715083830685406</v>
       </c>
       <c r="C27">
-        <v>269.3485756417265</v>
+        <v>267.3844305368983</v>
       </c>
       <c r="D27">
-        <v>329.4235756417265</v>
+        <v>331.1944305368983</v>
       </c>
       <c r="E27">
-        <v>-192.425</v>
+        <v>-188.69</v>
       </c>
       <c r="F27">
-        <v>93.375</v>
+        <v>97.11</v>
       </c>
       <c r="G27">
         <v>33.3</v>
@@ -3501,28 +3501,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M27">
-        <v>4.6967625</v>
+        <v>4.884633</v>
       </c>
       <c r="N27">
-        <v>70.02823749999999</v>
+        <v>69.840367</v>
       </c>
       <c r="O27">
-        <v>20.6583300625</v>
+        <v>20.602908265</v>
       </c>
       <c r="P27">
-        <v>49.36990743749999</v>
+        <v>49.237458735</v>
       </c>
       <c r="Q27">
-        <v>81.2699074375</v>
+        <v>81.137458735</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1180820076453642</v>
+        <v>0.1188254706849379</v>
       </c>
       <c r="T27">
-        <v>1.118179669840652</v>
+        <v>1.129680806613277</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.90989538006233</v>
+        <v>15.29797632698301</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09715083830685406</v>
+        <v>0.09687479587968498</v>
       </c>
       <c r="C28">
-        <v>267.3844305368983</v>
+        <v>265.4394272054244</v>
       </c>
       <c r="D28">
-        <v>331.1944305368983</v>
+        <v>332.9844272054244</v>
       </c>
       <c r="E28">
-        <v>-188.69</v>
+        <v>-184.955</v>
       </c>
       <c r="F28">
-        <v>97.11</v>
+        <v>100.845</v>
       </c>
       <c r="G28">
         <v>33.3</v>
@@ -3583,28 +3583,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M28">
-        <v>4.884633</v>
+        <v>5.072503500000001</v>
       </c>
       <c r="N28">
-        <v>69.840367</v>
+        <v>69.6524965</v>
       </c>
       <c r="O28">
-        <v>20.602908265</v>
+        <v>20.5474864675</v>
       </c>
       <c r="P28">
-        <v>49.237458735</v>
+        <v>49.1050100325</v>
       </c>
       <c r="Q28">
-        <v>81.137458735</v>
+        <v>81.0050100325</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1188254706849379</v>
+        <v>0.1195893025749109</v>
       </c>
       <c r="T28">
-        <v>1.129680806613277</v>
+        <v>1.141497043023509</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.29797632698301</v>
+        <v>14.73138461116882</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09687479587968498</v>
+        <v>0.09659875345251588</v>
       </c>
       <c r="C29">
-        <v>265.4394272054244</v>
+        <v>263.5138776987562</v>
       </c>
       <c r="D29">
-        <v>332.9844272054244</v>
+        <v>334.7938776987562</v>
       </c>
       <c r="E29">
-        <v>-184.955</v>
+        <v>-181.22</v>
       </c>
       <c r="F29">
-        <v>100.845</v>
+        <v>104.58</v>
       </c>
       <c r="G29">
         <v>33.3</v>
@@ -3665,28 +3665,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M29">
-        <v>5.072503500000001</v>
+        <v>5.260374000000001</v>
       </c>
       <c r="N29">
-        <v>69.6524965</v>
+        <v>69.464626</v>
       </c>
       <c r="O29">
-        <v>20.5474864675</v>
+        <v>20.49206467</v>
       </c>
       <c r="P29">
-        <v>49.1050100325</v>
+        <v>48.97256133</v>
       </c>
       <c r="Q29">
-        <v>81.0050100325</v>
+        <v>80.87256133</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1195893025749109</v>
+        <v>0.1203743520173832</v>
       </c>
       <c r="T29">
-        <v>1.141497043023509</v>
+        <v>1.153641508222913</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.73138461116882</v>
+        <v>14.20526373219851</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09659875345251588</v>
+        <v>0.0963227110253468</v>
       </c>
       <c r="C30">
-        <v>263.5138776987562</v>
+        <v>261.6081008882036</v>
       </c>
       <c r="D30">
-        <v>334.7938776987562</v>
+        <v>336.6231008882036</v>
       </c>
       <c r="E30">
-        <v>-181.22</v>
+        <v>-177.485</v>
       </c>
       <c r="F30">
-        <v>104.58</v>
+        <v>108.315</v>
       </c>
       <c r="G30">
         <v>33.3</v>
@@ -3747,28 +3747,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M30">
-        <v>5.260374000000001</v>
+        <v>5.4482445</v>
       </c>
       <c r="N30">
-        <v>69.464626</v>
+        <v>69.27675549999999</v>
       </c>
       <c r="O30">
-        <v>20.49206467</v>
+        <v>20.4366428725</v>
       </c>
       <c r="P30">
-        <v>48.97256133</v>
+        <v>48.84011262749999</v>
       </c>
       <c r="Q30">
-        <v>80.87256133</v>
+        <v>80.7401126275</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1203743520173832</v>
+        <v>0.1211815155286575</v>
       </c>
       <c r="T30">
-        <v>1.153641508222913</v>
+        <v>1.166128071033568</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.20526373219851</v>
+        <v>13.71542705177787</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0963227110253468</v>
+        <v>0.0960466685981777</v>
       </c>
       <c r="C31">
-        <v>261.6081008882036</v>
+        <v>259.7224226522686</v>
       </c>
       <c r="D31">
-        <v>336.6231008882036</v>
+        <v>338.4724226522686</v>
       </c>
       <c r="E31">
-        <v>-177.485</v>
+        <v>-173.75</v>
       </c>
       <c r="F31">
-        <v>108.315</v>
+        <v>112.05</v>
       </c>
       <c r="G31">
         <v>33.3</v>
@@ -3829,28 +3829,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M31">
-        <v>5.448244499999999</v>
+        <v>5.636114999999999</v>
       </c>
       <c r="N31">
-        <v>69.27675549999999</v>
+        <v>69.08888499999999</v>
       </c>
       <c r="O31">
-        <v>20.4366428725</v>
+        <v>20.381221075</v>
       </c>
       <c r="P31">
-        <v>48.84011262749999</v>
+        <v>48.70766392499999</v>
       </c>
       <c r="Q31">
-        <v>80.7401126275</v>
+        <v>80.607663925</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1211815155286575</v>
+        <v>0.1220117408545396</v>
       </c>
       <c r="T31">
-        <v>1.166128071033568</v>
+        <v>1.178971392781671</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.71542705177787</v>
+        <v>13.25824615005194</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0960466685981777</v>
+        <v>0.09609845117100863</v>
       </c>
       <c r="C32">
-        <v>259.7224226522686</v>
+        <v>255.6389631576082</v>
       </c>
       <c r="D32">
-        <v>338.4724226522686</v>
+        <v>338.1239631576082</v>
       </c>
       <c r="E32">
-        <v>-173.75</v>
+        <v>-170.015</v>
       </c>
       <c r="F32">
-        <v>112.05</v>
+        <v>115.785</v>
       </c>
       <c r="G32">
         <v>33.3</v>
@@ -3911,45 +3911,45 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M32">
-        <v>5.636114999999999</v>
+        <v>5.997662999999999</v>
       </c>
       <c r="N32">
-        <v>69.08888499999999</v>
+        <v>68.72733699999999</v>
       </c>
       <c r="O32">
-        <v>20.381221075</v>
+        <v>20.274564415</v>
       </c>
       <c r="P32">
-        <v>48.70766392499999</v>
+        <v>48.45277258499999</v>
       </c>
       <c r="Q32">
-        <v>80.607663925</v>
+        <v>80.352772585</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1220117408545396</v>
+        <v>0.1228660306826212</v>
       </c>
       <c r="T32">
-        <v>1.178971392781671</v>
+        <v>1.19218698472537</v>
       </c>
       <c r="U32">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V32">
         <v>0.295</v>
       </c>
       <c r="W32">
-        <v>0.0354615</v>
+        <v>0.036519</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y32">
-        <v>13.25824615005194</v>
+        <v>12.45901945474429</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09609845117100863</v>
+        <v>0.09583298374383953</v>
       </c>
       <c r="C33">
-        <v>255.6389631576082</v>
+        <v>253.6979976493992</v>
       </c>
       <c r="D33">
-        <v>338.1239631576082</v>
+        <v>339.9179976493992</v>
       </c>
       <c r="E33">
-        <v>-170.015</v>
+        <v>-166.28</v>
       </c>
       <c r="F33">
-        <v>115.785</v>
+        <v>119.52</v>
       </c>
       <c r="G33">
         <v>33.3</v>
@@ -3993,28 +3993,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M33">
-        <v>5.997662999999999</v>
+        <v>6.191135999999999</v>
       </c>
       <c r="N33">
-        <v>68.72733699999999</v>
+        <v>68.53386399999999</v>
       </c>
       <c r="O33">
-        <v>20.274564415</v>
+        <v>20.21748988</v>
       </c>
       <c r="P33">
-        <v>48.45277258499999</v>
+        <v>48.31637411999999</v>
       </c>
       <c r="Q33">
-        <v>80.352772585</v>
+        <v>80.21637411999998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1228660306826212</v>
+        <v>0.123745446682117</v>
       </c>
       <c r="T33">
-        <v>1.19218698472537</v>
+        <v>1.205791270549767</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.45901945474429</v>
+        <v>12.06967509678353</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09583298374383953</v>
+        <v>0.09556751631667044</v>
       </c>
       <c r="C34">
-        <v>253.6979976493992</v>
+        <v>251.7761714415225</v>
       </c>
       <c r="D34">
-        <v>339.9179976493992</v>
+        <v>341.7311714415225</v>
       </c>
       <c r="E34">
-        <v>-166.28</v>
+        <v>-162.545</v>
       </c>
       <c r="F34">
-        <v>119.52</v>
+        <v>123.255</v>
       </c>
       <c r="G34">
         <v>33.3</v>
@@ -4075,28 +4075,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M34">
-        <v>6.191135999999999</v>
+        <v>6.384609</v>
       </c>
       <c r="N34">
-        <v>68.53386399999999</v>
+        <v>68.340391</v>
       </c>
       <c r="O34">
-        <v>20.21748988</v>
+        <v>20.160415345</v>
       </c>
       <c r="P34">
-        <v>48.31637411999999</v>
+        <v>48.179975655</v>
       </c>
       <c r="Q34">
-        <v>80.21637411999998</v>
+        <v>80.079975655</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.123745446682117</v>
+        <v>0.1246511139054783</v>
       </c>
       <c r="T34">
-        <v>1.205791270549767</v>
+        <v>1.219801654458474</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.06967509678353</v>
+        <v>11.70392736657797</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09556751631667044</v>
+        <v>0.09530204888950135</v>
       </c>
       <c r="C35">
-        <v>251.7761714415225</v>
+        <v>249.8737924521914</v>
       </c>
       <c r="D35">
-        <v>341.7311714415225</v>
+        <v>343.5637924521914</v>
       </c>
       <c r="E35">
-        <v>-162.545</v>
+        <v>-158.81</v>
       </c>
       <c r="F35">
-        <v>123.255</v>
+        <v>126.99</v>
       </c>
       <c r="G35">
         <v>33.3</v>
@@ -4157,28 +4157,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M35">
-        <v>6.384609</v>
+        <v>6.578082</v>
       </c>
       <c r="N35">
-        <v>68.340391</v>
+        <v>68.146918</v>
       </c>
       <c r="O35">
-        <v>20.160415345</v>
+        <v>20.10334081</v>
       </c>
       <c r="P35">
-        <v>48.179975655</v>
+        <v>48.04357719</v>
       </c>
       <c r="Q35">
-        <v>80.079975655</v>
+        <v>79.94357719</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1246511139054783</v>
+        <v>0.1255842255901536</v>
       </c>
       <c r="T35">
-        <v>1.219801654458474</v>
+        <v>1.234236595455324</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.70392736657797</v>
+        <v>11.35969420873744</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09530204888950135</v>
+        <v>0.09503658146233226</v>
       </c>
       <c r="C36">
-        <v>249.8737924521914</v>
+        <v>247.9911752403935</v>
       </c>
       <c r="D36">
-        <v>343.5637924521914</v>
+        <v>345.4161752403936</v>
       </c>
       <c r="E36">
-        <v>-158.81</v>
+        <v>-155.075</v>
       </c>
       <c r="F36">
-        <v>126.99</v>
+        <v>130.725</v>
       </c>
       <c r="G36">
         <v>33.3</v>
@@ -4239,28 +4239,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M36">
-        <v>6.578082</v>
+        <v>6.771555000000001</v>
       </c>
       <c r="N36">
-        <v>68.146918</v>
+        <v>67.95344499999999</v>
       </c>
       <c r="O36">
-        <v>20.10334081</v>
+        <v>20.046266275</v>
       </c>
       <c r="P36">
-        <v>48.04357719</v>
+        <v>47.90717872499999</v>
       </c>
       <c r="Q36">
-        <v>79.94357719</v>
+        <v>79.807178725</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1255842255901536</v>
+        <v>0.1265460484035881</v>
       </c>
       <c r="T36">
-        <v>1.234236595455324</v>
+        <v>1.249115688482846</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.35969420873744</v>
+        <v>11.03513151705922</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09503658146233226</v>
+        <v>0.09477111403516318</v>
       </c>
       <c r="C37">
-        <v>247.9911752403935</v>
+        <v>246.1286411858856</v>
       </c>
       <c r="D37">
-        <v>345.4161752403936</v>
+        <v>347.2886411858856</v>
       </c>
       <c r="E37">
-        <v>-155.075</v>
+        <v>-151.34</v>
       </c>
       <c r="F37">
-        <v>130.725</v>
+        <v>134.46</v>
       </c>
       <c r="G37">
         <v>33.3</v>
@@ -4321,28 +4321,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M37">
-        <v>6.771555000000001</v>
+        <v>6.965028</v>
       </c>
       <c r="N37">
-        <v>67.95344499999999</v>
+        <v>67.75997199999999</v>
       </c>
       <c r="O37">
-        <v>20.046266275</v>
+        <v>19.98919174</v>
       </c>
       <c r="P37">
-        <v>47.90717872499999</v>
+        <v>47.77078026</v>
       </c>
       <c r="Q37">
-        <v>79.807178725</v>
+        <v>79.67078025999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1265460484035881</v>
+        <v>0.1275379281799425</v>
       </c>
       <c r="T37">
-        <v>1.249115688482846</v>
+        <v>1.264459753167478</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.03513151705922</v>
+        <v>10.7286000860298</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0947711140351632</v>
+        <v>0.0945056466079941</v>
       </c>
       <c r="C38">
-        <v>246.1286411858855</v>
+        <v>244.2865186750746</v>
       </c>
       <c r="D38">
-        <v>347.2886411858855</v>
+        <v>349.1815186750746</v>
       </c>
       <c r="E38">
-        <v>-151.34</v>
+        <v>-147.605</v>
       </c>
       <c r="F38">
-        <v>134.46</v>
+        <v>138.195</v>
       </c>
       <c r="G38">
         <v>33.3</v>
@@ -4403,28 +4403,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M38">
-        <v>6.965028</v>
+        <v>7.158500999999999</v>
       </c>
       <c r="N38">
-        <v>67.75997199999999</v>
+        <v>67.56649899999999</v>
       </c>
       <c r="O38">
-        <v>19.98919174</v>
+        <v>19.932117205</v>
       </c>
       <c r="P38">
-        <v>47.77078026</v>
+        <v>47.634381795</v>
       </c>
       <c r="Q38">
-        <v>79.67078025999999</v>
+        <v>79.534381795</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1275379281799425</v>
+        <v>0.1285612962031652</v>
       </c>
       <c r="T38">
-        <v>1.264459753167478</v>
+        <v>1.280290931016702</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.7286000860298</v>
+        <v>10.43863792154251</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0945056466079941</v>
+        <v>0.094240179180825</v>
       </c>
       <c r="C39">
-        <v>244.2865186750746</v>
+        <v>242.4651432930108</v>
       </c>
       <c r="D39">
-        <v>349.1815186750746</v>
+        <v>351.0951432930108</v>
       </c>
       <c r="E39">
-        <v>-147.605</v>
+        <v>-143.87</v>
       </c>
       <c r="F39">
-        <v>138.195</v>
+        <v>141.93</v>
       </c>
       <c r="G39">
         <v>33.3</v>
@@ -4485,28 +4485,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M39">
-        <v>7.158500999999999</v>
+        <v>7.351974</v>
       </c>
       <c r="N39">
-        <v>67.56649899999999</v>
+        <v>67.373026</v>
       </c>
       <c r="O39">
-        <v>19.932117205</v>
+        <v>19.87504267</v>
       </c>
       <c r="P39">
-        <v>47.634381795</v>
+        <v>47.49798333</v>
       </c>
       <c r="Q39">
-        <v>79.534381795</v>
+        <v>79.39798332999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1285612962031652</v>
+        <v>0.1296176760981048</v>
       </c>
       <c r="T39">
-        <v>1.280290931016702</v>
+        <v>1.296632792022352</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.43863792154251</v>
+        <v>10.16393692360718</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.094240179180825</v>
+        <v>0.09397471175365592</v>
       </c>
       <c r="C40">
-        <v>242.4651432930108</v>
+        <v>240.6648580217291</v>
       </c>
       <c r="D40">
-        <v>351.0951432930108</v>
+        <v>353.0298580217291</v>
       </c>
       <c r="E40">
-        <v>-143.87</v>
+        <v>-140.135</v>
       </c>
       <c r="F40">
-        <v>141.93</v>
+        <v>145.665</v>
       </c>
       <c r="G40">
         <v>33.3</v>
@@ -4567,28 +4567,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M40">
-        <v>7.351974</v>
+        <v>7.545446999999999</v>
       </c>
       <c r="N40">
-        <v>67.373026</v>
+        <v>67.179553</v>
       </c>
       <c r="O40">
-        <v>19.87504267</v>
+        <v>19.817968135</v>
       </c>
       <c r="P40">
-        <v>47.49798333</v>
+        <v>47.361584865</v>
       </c>
       <c r="Q40">
-        <v>79.39798332999999</v>
+        <v>79.261584865</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1296176760981048</v>
+        <v>0.1307086913994359</v>
       </c>
       <c r="T40">
-        <v>1.296632792022352</v>
+        <v>1.313510451749499</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.16393692360718</v>
+        <v>9.903323156335205</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09397471175365592</v>
+        <v>0.09418864432648684</v>
       </c>
       <c r="C41">
-        <v>240.6648580217291</v>
+        <v>235.3690665000005</v>
       </c>
       <c r="D41">
-        <v>353.0298580217291</v>
+        <v>351.4690665000005</v>
       </c>
       <c r="E41">
-        <v>-140.135</v>
+        <v>-136.4</v>
       </c>
       <c r="F41">
-        <v>145.665</v>
+        <v>149.4</v>
       </c>
       <c r="G41">
         <v>33.3</v>
@@ -4649,45 +4649,45 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M41">
-        <v>7.545446999999999</v>
+        <v>7.992900000000001</v>
       </c>
       <c r="N41">
-        <v>67.179553</v>
+        <v>66.73209999999999</v>
       </c>
       <c r="O41">
-        <v>19.817968135</v>
+        <v>19.6859695</v>
       </c>
       <c r="P41">
-        <v>47.361584865</v>
+        <v>47.04613049999999</v>
       </c>
       <c r="Q41">
-        <v>79.261584865</v>
+        <v>78.94613049999998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1307086913994359</v>
+        <v>0.1318360738774781</v>
       </c>
       <c r="T41">
-        <v>1.313510451749499</v>
+        <v>1.330950700134218</v>
       </c>
       <c r="U41">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V41">
         <v>0.295</v>
       </c>
       <c r="W41">
-        <v>0.036519</v>
+        <v>0.0377175</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>9.903323156335205</v>
+        <v>9.348922168424474</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09418864432648684</v>
+        <v>0.09393516189931773</v>
       </c>
       <c r="C42">
-        <v>235.3690665000005</v>
+        <v>233.4849220603833</v>
       </c>
       <c r="D42">
-        <v>351.4690665000005</v>
+        <v>353.3199220603833</v>
       </c>
       <c r="E42">
-        <v>-136.4</v>
+        <v>-132.665</v>
       </c>
       <c r="F42">
-        <v>149.4</v>
+        <v>153.135</v>
       </c>
       <c r="G42">
         <v>33.3</v>
@@ -4731,28 +4731,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M42">
-        <v>7.992900000000001</v>
+        <v>8.1927225</v>
       </c>
       <c r="N42">
-        <v>66.73209999999999</v>
+        <v>66.53227749999999</v>
       </c>
       <c r="O42">
-        <v>19.6859695</v>
+        <v>19.6270218625</v>
       </c>
       <c r="P42">
-        <v>47.04613049999999</v>
+        <v>46.90525563749999</v>
       </c>
       <c r="Q42">
-        <v>78.94613049999998</v>
+        <v>78.80525563749998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1318360738774781</v>
+        <v>0.133001672710708</v>
       </c>
       <c r="T42">
-        <v>1.330950700134218</v>
+        <v>1.348982143379435</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.348922168424474</v>
+        <v>9.120899676511684</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09393516189931773</v>
+        <v>0.09368167947214864</v>
       </c>
       <c r="C43">
-        <v>233.4849220603833</v>
+        <v>231.6203742332891</v>
       </c>
       <c r="D43">
-        <v>353.3199220603833</v>
+        <v>355.1903742332891</v>
       </c>
       <c r="E43">
-        <v>-132.665</v>
+        <v>-128.93</v>
       </c>
       <c r="F43">
-        <v>153.135</v>
+        <v>156.87</v>
       </c>
       <c r="G43">
         <v>33.3</v>
@@ -4813,28 +4813,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M43">
-        <v>8.1927225</v>
+        <v>8.392545</v>
       </c>
       <c r="N43">
-        <v>66.53227749999999</v>
+        <v>66.332455</v>
       </c>
       <c r="O43">
-        <v>19.6270218625</v>
+        <v>19.568074225</v>
       </c>
       <c r="P43">
-        <v>46.90525563749999</v>
+        <v>46.764380775</v>
       </c>
       <c r="Q43">
-        <v>78.80525563749998</v>
+        <v>78.664380775</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.133001672710708</v>
+        <v>0.1342074646071528</v>
       </c>
       <c r="T43">
-        <v>1.348982143379435</v>
+        <v>1.36763536052966</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.120899676511684</v>
+        <v>8.903735398499501</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09368167947214866</v>
+        <v>0.09342819704497957</v>
       </c>
       <c r="C44">
-        <v>231.620374233289</v>
+        <v>229.7757359046058</v>
       </c>
       <c r="D44">
-        <v>355.190374233289</v>
+        <v>357.0807359046058</v>
       </c>
       <c r="E44">
-        <v>-128.93</v>
+        <v>-125.195</v>
       </c>
       <c r="F44">
-        <v>156.87</v>
+        <v>160.605</v>
       </c>
       <c r="G44">
         <v>33.3</v>
@@ -4895,28 +4895,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M44">
-        <v>8.392545</v>
+        <v>8.5923675</v>
       </c>
       <c r="N44">
-        <v>66.332455</v>
+        <v>66.1326325</v>
       </c>
       <c r="O44">
-        <v>19.568074225</v>
+        <v>19.5091265875</v>
       </c>
       <c r="P44">
-        <v>46.764380775</v>
+        <v>46.6235059125</v>
       </c>
       <c r="Q44">
-        <v>78.664380775</v>
+        <v>78.5235059125</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1342074646071528</v>
+        <v>0.1354555649911922</v>
       </c>
       <c r="T44">
-        <v>1.36763536052966</v>
+        <v>1.386943076527261</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.903735398499501</v>
+        <v>8.696671784580909</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09342819704497957</v>
+        <v>0.09317471461781049</v>
       </c>
       <c r="C45">
-        <v>229.7757359046058</v>
+        <v>227.9513266567111</v>
       </c>
       <c r="D45">
-        <v>357.0807359046058</v>
+        <v>358.9913266567111</v>
       </c>
       <c r="E45">
-        <v>-125.195</v>
+        <v>-121.46</v>
       </c>
       <c r="F45">
-        <v>160.605</v>
+        <v>164.34</v>
       </c>
       <c r="G45">
         <v>33.3</v>
@@ -4977,28 +4977,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M45">
-        <v>8.5923675</v>
+        <v>8.79219</v>
       </c>
       <c r="N45">
-        <v>66.1326325</v>
+        <v>65.93280999999999</v>
       </c>
       <c r="O45">
-        <v>19.5091265875</v>
+        <v>19.45017894999999</v>
       </c>
       <c r="P45">
-        <v>46.6235059125</v>
+        <v>46.48263104999999</v>
       </c>
       <c r="Q45">
-        <v>78.5235059125</v>
+        <v>78.38263104999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1354555649911922</v>
+        <v>0.1367482403889473</v>
       </c>
       <c r="T45">
-        <v>1.386943076527261</v>
+        <v>1.406940353810491</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.696671784580909</v>
+        <v>8.499020153113159</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09317471461781049</v>
+        <v>0.09292123219064138</v>
       </c>
       <c r="C46">
-        <v>227.9513266567111</v>
+        <v>226.1474729485874</v>
       </c>
       <c r="D46">
-        <v>358.9913266567111</v>
+        <v>360.9224729485874</v>
       </c>
       <c r="E46">
-        <v>-121.46</v>
+        <v>-117.725</v>
       </c>
       <c r="F46">
-        <v>164.34</v>
+        <v>168.075</v>
       </c>
       <c r="G46">
         <v>33.3</v>
@@ -5059,28 +5059,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M46">
-        <v>8.79219</v>
+        <v>8.992012500000001</v>
       </c>
       <c r="N46">
-        <v>65.93280999999999</v>
+        <v>65.73298749999999</v>
       </c>
       <c r="O46">
-        <v>19.45017894999999</v>
+        <v>19.3912313125</v>
       </c>
       <c r="P46">
-        <v>46.48263104999999</v>
+        <v>46.3417561875</v>
       </c>
       <c r="Q46">
-        <v>78.38263104999999</v>
+        <v>78.24175618749999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1367482403889473</v>
+        <v>0.1380879221648025</v>
       </c>
       <c r="T46">
-        <v>1.406940353810491</v>
+        <v>1.427664804813111</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.499020153113159</v>
+        <v>8.310153038599534</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09292123219064138</v>
+        <v>0.09266774976347231</v>
       </c>
       <c r="C47">
-        <v>226.1474729485874</v>
+        <v>224.3645083017799</v>
       </c>
       <c r="D47">
-        <v>360.9224729485874</v>
+        <v>362.8745083017799</v>
       </c>
       <c r="E47">
-        <v>-117.725</v>
+        <v>-113.99</v>
       </c>
       <c r="F47">
-        <v>168.075</v>
+        <v>171.81</v>
       </c>
       <c r="G47">
         <v>33.3</v>
@@ -5141,28 +5141,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M47">
-        <v>8.992012500000001</v>
+        <v>9.191834999999999</v>
       </c>
       <c r="N47">
-        <v>65.73298749999999</v>
+        <v>65.533165</v>
       </c>
       <c r="O47">
-        <v>19.3912313125</v>
+        <v>19.332283675</v>
       </c>
       <c r="P47">
-        <v>46.3417561875</v>
+        <v>46.200881325</v>
       </c>
       <c r="Q47">
-        <v>78.24175618749999</v>
+        <v>78.10088132499999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1380879221648025</v>
+        <v>0.139477221784208</v>
       </c>
       <c r="T47">
-        <v>1.427664804813111</v>
+        <v>1.449156828075087</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.310153038599534</v>
+        <v>8.129497537760415</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09266774976347231</v>
+        <v>0.09241426733630322</v>
       </c>
       <c r="C48">
-        <v>224.3645083017799</v>
+        <v>222.6027734924244</v>
       </c>
       <c r="D48">
-        <v>362.8745083017799</v>
+        <v>364.8477734924244</v>
       </c>
       <c r="E48">
-        <v>-113.99</v>
+        <v>-110.255</v>
       </c>
       <c r="F48">
-        <v>171.81</v>
+        <v>175.545</v>
       </c>
       <c r="G48">
         <v>33.3</v>
@@ -5223,28 +5223,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M48">
-        <v>9.191834999999999</v>
+        <v>9.391657500000001</v>
       </c>
       <c r="N48">
-        <v>65.533165</v>
+        <v>65.33334249999999</v>
       </c>
       <c r="O48">
-        <v>19.332283675</v>
+        <v>19.27333603749999</v>
       </c>
       <c r="P48">
-        <v>46.200881325</v>
+        <v>46.06000646249999</v>
       </c>
       <c r="Q48">
-        <v>78.10088132499999</v>
+        <v>77.96000646249999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.139477221784208</v>
+        <v>0.1409189478043457</v>
       </c>
       <c r="T48">
-        <v>1.449156828075087</v>
+        <v>1.471459871082798</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.129497537760415</v>
+        <v>7.956529505042106</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09241426733630322</v>
+        <v>0.09216078490913412</v>
       </c>
       <c r="C49">
-        <v>222.6027734924244</v>
+        <v>220.8626167495729</v>
       </c>
       <c r="D49">
-        <v>364.8477734924244</v>
+        <v>366.8426167495729</v>
       </c>
       <c r="E49">
-        <v>-110.255</v>
+        <v>-106.52</v>
       </c>
       <c r="F49">
-        <v>175.545</v>
+        <v>179.28</v>
       </c>
       <c r="G49">
         <v>33.3</v>
@@ -5305,28 +5305,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M49">
-        <v>9.391657500000001</v>
+        <v>9.591480000000001</v>
       </c>
       <c r="N49">
-        <v>65.33334249999999</v>
+        <v>65.13351999999999</v>
       </c>
       <c r="O49">
-        <v>19.27333603749999</v>
+        <v>19.2143884</v>
       </c>
       <c r="P49">
-        <v>46.06000646249999</v>
+        <v>45.91913159999999</v>
       </c>
       <c r="Q49">
-        <v>77.96000646249999</v>
+        <v>77.81913159999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1409189478043457</v>
+        <v>0.1424161248252579</v>
       </c>
       <c r="T49">
-        <v>1.471459871082798</v>
+        <v>1.49462072343696</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.956529505042106</v>
+        <v>7.790768473687063</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09216078490913412</v>
+        <v>0.09190730248196502</v>
       </c>
       <c r="C50">
-        <v>220.8626167495729</v>
+        <v>219.1443939600619</v>
       </c>
       <c r="D50">
-        <v>366.8426167495729</v>
+        <v>368.8593939600619</v>
       </c>
       <c r="E50">
-        <v>-106.52</v>
+        <v>-102.785</v>
       </c>
       <c r="F50">
-        <v>179.28</v>
+        <v>183.015</v>
       </c>
       <c r="G50">
         <v>33.3</v>
@@ -5387,28 +5387,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M50">
-        <v>9.591480000000001</v>
+        <v>9.791302499999999</v>
       </c>
       <c r="N50">
-        <v>65.13351999999999</v>
+        <v>64.93369749999999</v>
       </c>
       <c r="O50">
-        <v>19.2143884</v>
+        <v>19.1554407625</v>
       </c>
       <c r="P50">
-        <v>45.91913159999999</v>
+        <v>45.7782567375</v>
       </c>
       <c r="Q50">
-        <v>77.81913159999999</v>
+        <v>77.67825673749999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1424161248252579</v>
+        <v>0.1439720146705196</v>
       </c>
       <c r="T50">
-        <v>1.49462072343696</v>
+        <v>1.518689844510893</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.790768473687063</v>
+        <v>7.631773198713859</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09190730248196502</v>
+        <v>0.09193582005479595</v>
       </c>
       <c r="C51">
-        <v>219.1443939600619</v>
+        <v>215.1813937940491</v>
       </c>
       <c r="D51">
-        <v>368.8593939600619</v>
+        <v>368.6313937940491</v>
       </c>
       <c r="E51">
-        <v>-102.785</v>
+        <v>-99.05000000000001</v>
       </c>
       <c r="F51">
-        <v>183.015</v>
+        <v>186.75</v>
       </c>
       <c r="G51">
         <v>33.3</v>
@@ -5469,45 +5469,45 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M51">
-        <v>9.791302499999999</v>
+        <v>10.140525</v>
       </c>
       <c r="N51">
-        <v>64.93369749999999</v>
+        <v>64.584475</v>
       </c>
       <c r="O51">
-        <v>19.1554407625</v>
+        <v>19.052420125</v>
       </c>
       <c r="P51">
-        <v>45.7782567375</v>
+        <v>45.532054875</v>
       </c>
       <c r="Q51">
-        <v>77.67825673749999</v>
+        <v>77.43205487500001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1439720146705196</v>
+        <v>0.1455901401095919</v>
       </c>
       <c r="T51">
-        <v>1.518689844510893</v>
+        <v>1.543721730427783</v>
       </c>
       <c r="U51">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V51">
         <v>0.295</v>
       </c>
       <c r="W51">
-        <v>0.0377175</v>
+        <v>0.0382815</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y51">
-        <v>7.631773198713859</v>
+        <v>7.368947860194615</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09193582005479595</v>
+        <v>0.09168797762762686</v>
       </c>
       <c r="C52">
-        <v>215.1813937940491</v>
+        <v>213.4373836805512</v>
       </c>
       <c r="D52">
-        <v>368.6313937940491</v>
+        <v>370.6223836805513</v>
       </c>
       <c r="E52">
-        <v>-99.05000000000001</v>
+        <v>-95.315</v>
       </c>
       <c r="F52">
-        <v>186.75</v>
+        <v>190.485</v>
       </c>
       <c r="G52">
         <v>33.3</v>
@@ -5551,28 +5551,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M52">
-        <v>10.140525</v>
+        <v>10.3433355</v>
       </c>
       <c r="N52">
-        <v>64.584475</v>
+        <v>64.3816645</v>
       </c>
       <c r="O52">
-        <v>19.052420125</v>
+        <v>18.9925910275</v>
       </c>
       <c r="P52">
-        <v>45.532054875</v>
+        <v>45.3890734725</v>
       </c>
       <c r="Q52">
-        <v>77.43205487500001</v>
+        <v>77.28907347250001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1455901401095919</v>
+        <v>0.1472743114849528</v>
       </c>
       <c r="T52">
-        <v>1.543721730427783</v>
+        <v>1.569775325973934</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.368947860194615</v>
+        <v>7.224458686465309</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09168797762762686</v>
+        <v>0.09144013520045775</v>
       </c>
       <c r="C53">
-        <v>213.4373836805512</v>
+        <v>211.7149971561938</v>
       </c>
       <c r="D53">
-        <v>370.6223836805513</v>
+        <v>372.6349971561938</v>
       </c>
       <c r="E53">
-        <v>-95.315</v>
+        <v>-91.58000000000001</v>
       </c>
       <c r="F53">
-        <v>190.485</v>
+        <v>194.22</v>
       </c>
       <c r="G53">
         <v>33.3</v>
@@ -5633,28 +5633,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M53">
-        <v>10.3433355</v>
+        <v>10.546146</v>
       </c>
       <c r="N53">
-        <v>64.3816645</v>
+        <v>64.178854</v>
       </c>
       <c r="O53">
-        <v>18.9925910275</v>
+        <v>18.93276193</v>
       </c>
       <c r="P53">
-        <v>45.3890734725</v>
+        <v>45.24609207</v>
       </c>
       <c r="Q53">
-        <v>77.28907347250001</v>
+        <v>77.14609207000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1472743114849528</v>
+        <v>0.1490286566676203</v>
       </c>
       <c r="T53">
-        <v>1.569775325973934</v>
+        <v>1.596914488001174</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.224458686465309</v>
+        <v>7.085526788648669</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09144013520045775</v>
+        <v>0.09119229277328869</v>
       </c>
       <c r="C54">
-        <v>211.7149971561938</v>
+        <v>210.0145884160932</v>
       </c>
       <c r="D54">
-        <v>372.6349971561938</v>
+        <v>374.6695884160932</v>
       </c>
       <c r="E54">
-        <v>-91.58000000000001</v>
+        <v>-87.845</v>
       </c>
       <c r="F54">
-        <v>194.22</v>
+        <v>197.955</v>
       </c>
       <c r="G54">
         <v>33.3</v>
@@ -5715,28 +5715,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M54">
-        <v>10.546146</v>
+        <v>10.7489565</v>
       </c>
       <c r="N54">
-        <v>64.178854</v>
+        <v>63.9760435</v>
       </c>
       <c r="O54">
-        <v>18.93276193</v>
+        <v>18.8729328325</v>
       </c>
       <c r="P54">
-        <v>45.24609207</v>
+        <v>45.1031106675</v>
       </c>
       <c r="Q54">
-        <v>77.14609207000001</v>
+        <v>77.0031106675</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1490286566676203</v>
+        <v>0.1508576548367844</v>
       </c>
       <c r="T54">
-        <v>1.596914488001174</v>
+        <v>1.625208507987021</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.085526788648669</v>
+        <v>6.951837603957183</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09119229277328869</v>
+        <v>0.09094445034611959</v>
       </c>
       <c r="C55">
-        <v>210.0145884160932</v>
+        <v>208.3365194334729</v>
       </c>
       <c r="D55">
-        <v>374.6695884160932</v>
+        <v>376.726519433473</v>
       </c>
       <c r="E55">
-        <v>-87.845</v>
+        <v>-84.10999999999999</v>
       </c>
       <c r="F55">
-        <v>197.955</v>
+        <v>201.69</v>
       </c>
       <c r="G55">
         <v>33.3</v>
@@ -5797,28 +5797,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M55">
-        <v>10.7489565</v>
+        <v>10.951767</v>
       </c>
       <c r="N55">
-        <v>63.9760435</v>
+        <v>63.77323299999999</v>
       </c>
       <c r="O55">
-        <v>18.8729328325</v>
+        <v>18.81310373499999</v>
       </c>
       <c r="P55">
-        <v>45.1031106675</v>
+        <v>44.96012926499999</v>
       </c>
       <c r="Q55">
-        <v>77.0031106675</v>
+        <v>76.86012926499998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1508576548367844</v>
+        <v>0.1527661746654774</v>
       </c>
       <c r="T55">
-        <v>1.625208507987021</v>
+        <v>1.654732702754861</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.951837603957183</v>
+        <v>6.823099870550568</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09094445034611959</v>
+        <v>0.0906966079189505</v>
       </c>
       <c r="C56">
-        <v>208.3365194334729</v>
+        <v>206.6811601743482</v>
       </c>
       <c r="D56">
-        <v>376.726519433473</v>
+        <v>378.8061601743482</v>
       </c>
       <c r="E56">
-        <v>-84.10999999999999</v>
+        <v>-80.375</v>
       </c>
       <c r="F56">
-        <v>201.69</v>
+        <v>205.425</v>
       </c>
       <c r="G56">
         <v>33.3</v>
@@ -5879,28 +5879,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M56">
-        <v>10.951767</v>
+        <v>11.1545775</v>
       </c>
       <c r="N56">
-        <v>63.77323299999999</v>
+        <v>63.57042249999999</v>
       </c>
       <c r="O56">
-        <v>18.81310373499999</v>
+        <v>18.7532746375</v>
       </c>
       <c r="P56">
-        <v>44.96012926499999</v>
+        <v>44.81714786249999</v>
       </c>
       <c r="Q56">
-        <v>76.86012926499998</v>
+        <v>76.71714786249998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1527661746654774</v>
+        <v>0.1547595175976678</v>
       </c>
       <c r="T56">
-        <v>1.654732702754861</v>
+        <v>1.685569083956826</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.823099870550568</v>
+        <v>6.699043509267831</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0906966079189505</v>
+        <v>0.09044876549178141</v>
       </c>
       <c r="C57">
-        <v>206.6811601743482</v>
+        <v>205.0488888193652</v>
       </c>
       <c r="D57">
-        <v>378.8061601743482</v>
+        <v>380.9088888193652</v>
       </c>
       <c r="E57">
-        <v>-80.375</v>
+        <v>-76.63999999999999</v>
       </c>
       <c r="F57">
-        <v>205.425</v>
+        <v>209.16</v>
       </c>
       <c r="G57">
         <v>33.3</v>
@@ -5961,28 +5961,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M57">
-        <v>11.1545775</v>
+        <v>11.357388</v>
       </c>
       <c r="N57">
-        <v>63.57042249999999</v>
+        <v>63.36761199999999</v>
       </c>
       <c r="O57">
-        <v>18.7532746375</v>
+        <v>18.69344554</v>
       </c>
       <c r="P57">
-        <v>44.81714786249999</v>
+        <v>44.67416646</v>
       </c>
       <c r="Q57">
-        <v>76.71714786249998</v>
+        <v>76.57416645999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1547595175976678</v>
+        <v>0.1568434670267759</v>
       </c>
       <c r="T57">
-        <v>1.685569083956826</v>
+        <v>1.717807118849791</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.699043509267831</v>
+        <v>6.579417732316619</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09044876549178141</v>
+        <v>0.09020092306461232</v>
       </c>
       <c r="C58">
-        <v>205.0488888193652</v>
+        <v>203.4400919930671</v>
       </c>
       <c r="D58">
-        <v>380.9088888193652</v>
+        <v>383.0350919930671</v>
       </c>
       <c r="E58">
-        <v>-76.63999999999999</v>
+        <v>-72.905</v>
       </c>
       <c r="F58">
-        <v>209.16</v>
+        <v>212.895</v>
       </c>
       <c r="G58">
         <v>33.3</v>
@@ -6043,28 +6043,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M58">
-        <v>11.357388</v>
+        <v>11.5601985</v>
       </c>
       <c r="N58">
-        <v>63.36761199999999</v>
+        <v>63.1648015</v>
       </c>
       <c r="O58">
-        <v>18.69344554</v>
+        <v>18.6336164425</v>
       </c>
       <c r="P58">
-        <v>44.67416646</v>
+        <v>44.5311850575</v>
       </c>
       <c r="Q58">
-        <v>76.57416645999999</v>
+        <v>76.43118505749999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1568434670267759</v>
+        <v>0.1590243443363077</v>
       </c>
       <c r="T58">
-        <v>1.717807118849791</v>
+        <v>1.751544597226149</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.579417732316619</v>
+        <v>6.463989351047908</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09020092306461232</v>
+        <v>0.08995308063744323</v>
       </c>
       <c r="C59">
-        <v>203.4400919930671</v>
+        <v>201.8551650008833</v>
       </c>
       <c r="D59">
-        <v>383.0350919930671</v>
+        <v>385.1851650008833</v>
       </c>
       <c r="E59">
-        <v>-72.905</v>
+        <v>-69.16999999999999</v>
       </c>
       <c r="F59">
-        <v>212.895</v>
+        <v>216.63</v>
       </c>
       <c r="G59">
         <v>33.3</v>
@@ -6125,28 +6125,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M59">
-        <v>11.5601985</v>
+        <v>11.763009</v>
       </c>
       <c r="N59">
-        <v>63.1648015</v>
+        <v>62.96199099999999</v>
       </c>
       <c r="O59">
-        <v>18.6336164425</v>
+        <v>18.573787345</v>
       </c>
       <c r="P59">
-        <v>44.5311850575</v>
+        <v>44.388203655</v>
       </c>
       <c r="Q59">
-        <v>76.43118505749999</v>
+        <v>76.28820365499999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1590243443363077</v>
+        <v>0.1613090729462934</v>
       </c>
       <c r="T59">
-        <v>1.751544597226149</v>
+        <v>1.786888622191858</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.463989351047908</v>
+        <v>6.35254125878846</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08995308063744323</v>
+        <v>0.08970523821027415</v>
       </c>
       <c r="C60">
-        <v>201.8551650008833</v>
+        <v>200.2945120741444</v>
       </c>
       <c r="D60">
-        <v>385.1851650008833</v>
+        <v>387.3595120741443</v>
       </c>
       <c r="E60">
-        <v>-69.17000000000002</v>
+        <v>-65.43500000000003</v>
       </c>
       <c r="F60">
-        <v>216.63</v>
+        <v>220.365</v>
       </c>
       <c r="G60">
         <v>33.3</v>
@@ -6207,28 +6207,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M60">
-        <v>11.763009</v>
+        <v>11.9658195</v>
       </c>
       <c r="N60">
-        <v>62.961991</v>
+        <v>62.7591805</v>
       </c>
       <c r="O60">
-        <v>18.573787345</v>
+        <v>18.5139582475</v>
       </c>
       <c r="P60">
-        <v>44.388203655</v>
+        <v>44.2452222525</v>
       </c>
       <c r="Q60">
-        <v>76.28820365499999</v>
+        <v>76.14522225249999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1613090729462934</v>
+        <v>0.163705251732376</v>
       </c>
       <c r="T60">
-        <v>1.786888622191857</v>
+        <v>1.823956745936381</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.352541258788461</v>
+        <v>6.244871067961538</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08970523821027415</v>
+        <v>0.08945739578310505</v>
       </c>
       <c r="C61">
-        <v>200.2945120741444</v>
+        <v>198.7585466234439</v>
       </c>
       <c r="D61">
-        <v>387.3595120741443</v>
+        <v>389.5585466234439</v>
       </c>
       <c r="E61">
-        <v>-65.43500000000003</v>
+        <v>-61.70000000000002</v>
       </c>
       <c r="F61">
-        <v>220.365</v>
+        <v>224.1</v>
       </c>
       <c r="G61">
         <v>33.3</v>
@@ -6289,28 +6289,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M61">
-        <v>11.9658195</v>
+        <v>12.16863</v>
       </c>
       <c r="N61">
-        <v>62.7591805</v>
+        <v>62.55636999999999</v>
       </c>
       <c r="O61">
-        <v>18.5139582475</v>
+        <v>18.45412915</v>
       </c>
       <c r="P61">
-        <v>44.2452222525</v>
+        <v>44.10224085</v>
       </c>
       <c r="Q61">
-        <v>76.14522225249999</v>
+        <v>76.00224084999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.163705251732376</v>
+        <v>0.1662212394577626</v>
       </c>
       <c r="T61">
-        <v>1.823956745936381</v>
+        <v>1.862878275868131</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.244871067961538</v>
+        <v>6.140789883495512</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08945739578310505</v>
+        <v>0.08963960335593596</v>
       </c>
       <c r="C62">
-        <v>198.7585466234439</v>
+        <v>193.4044508328297</v>
       </c>
       <c r="D62">
-        <v>389.5585466234439</v>
+        <v>387.9394508328297</v>
       </c>
       <c r="E62">
-        <v>-61.70000000000002</v>
+        <v>-57.965</v>
       </c>
       <c r="F62">
-        <v>224.1</v>
+        <v>227.835</v>
       </c>
       <c r="G62">
         <v>33.3</v>
@@ -6371,45 +6371,45 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M62">
-        <v>12.16863</v>
+        <v>12.5992755</v>
       </c>
       <c r="N62">
-        <v>62.55636999999999</v>
+        <v>62.12572449999999</v>
       </c>
       <c r="O62">
-        <v>18.45412915</v>
+        <v>18.32708872749999</v>
       </c>
       <c r="P62">
-        <v>44.10224085</v>
+        <v>43.79863577249999</v>
       </c>
       <c r="Q62">
-        <v>76.00224084999999</v>
+        <v>75.69863577249998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1662212394577626</v>
+        <v>0.1688662521947076</v>
       </c>
       <c r="T62">
-        <v>1.862878275868131</v>
+        <v>1.903795781693816</v>
       </c>
       <c r="U62">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V62">
         <v>0.295</v>
       </c>
       <c r="W62">
-        <v>0.0382815</v>
+        <v>0.03898650000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>6.140789883495512</v>
+        <v>5.930896582109026</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08963960335593596</v>
+        <v>0.08939881092876688</v>
       </c>
       <c r="C63">
-        <v>193.4044508328297</v>
+        <v>191.8120065578768</v>
       </c>
       <c r="D63">
-        <v>387.9394508328297</v>
+        <v>390.0820065578768</v>
       </c>
       <c r="E63">
-        <v>-57.965</v>
+        <v>-54.23000000000002</v>
       </c>
       <c r="F63">
-        <v>227.835</v>
+        <v>231.57</v>
       </c>
       <c r="G63">
         <v>33.3</v>
@@ -6453,28 +6453,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M63">
-        <v>12.5992755</v>
+        <v>12.805821</v>
       </c>
       <c r="N63">
-        <v>62.12572449999999</v>
+        <v>61.91917899999999</v>
       </c>
       <c r="O63">
-        <v>18.32708872749999</v>
+        <v>18.266157805</v>
       </c>
       <c r="P63">
-        <v>43.79863577249999</v>
+        <v>43.65302119499999</v>
       </c>
       <c r="Q63">
-        <v>75.69863577249998</v>
+        <v>75.55302119499999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1688662521947076</v>
+        <v>0.1716504761283339</v>
       </c>
       <c r="T63">
-        <v>1.903795781693816</v>
+        <v>1.946866840457696</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.930896582109026</v>
+        <v>5.835236959816945</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08939881092876688</v>
+        <v>0.08915801850159778</v>
       </c>
       <c r="C64">
-        <v>191.8120065578768</v>
+        <v>190.243360012212</v>
       </c>
       <c r="D64">
-        <v>390.0820065578768</v>
+        <v>392.2483600122119</v>
       </c>
       <c r="E64">
-        <v>-54.23000000000002</v>
+        <v>-50.495</v>
       </c>
       <c r="F64">
-        <v>231.57</v>
+        <v>235.305</v>
       </c>
       <c r="G64">
         <v>33.3</v>
@@ -6535,28 +6535,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M64">
-        <v>12.805821</v>
+        <v>13.0123665</v>
       </c>
       <c r="N64">
-        <v>61.91917899999999</v>
+        <v>61.7126335</v>
       </c>
       <c r="O64">
-        <v>18.266157805</v>
+        <v>18.2052268825</v>
       </c>
       <c r="P64">
-        <v>43.65302119499999</v>
+        <v>43.5074066175</v>
       </c>
       <c r="Q64">
-        <v>75.55302119499999</v>
+        <v>75.40740661749999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1716504761283339</v>
+        <v>0.174585198652967</v>
       </c>
       <c r="T64">
-        <v>1.946866840457696</v>
+        <v>1.992266064560164</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.835236959816945</v>
+        <v>5.742614150930962</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08915801850159778</v>
+        <v>0.08891722607442872</v>
       </c>
       <c r="C65">
-        <v>190.243360012212</v>
+        <v>188.698909898176</v>
       </c>
       <c r="D65">
-        <v>392.2483600122119</v>
+        <v>394.438909898176</v>
       </c>
       <c r="E65">
-        <v>-50.495</v>
+        <v>-46.76000000000002</v>
       </c>
       <c r="F65">
-        <v>235.305</v>
+        <v>239.04</v>
       </c>
       <c r="G65">
         <v>33.3</v>
@@ -6617,28 +6617,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M65">
-        <v>13.0123665</v>
+        <v>13.218912</v>
       </c>
       <c r="N65">
-        <v>61.7126335</v>
+        <v>61.50608799999999</v>
       </c>
       <c r="O65">
-        <v>18.2052268825</v>
+        <v>18.14429596</v>
       </c>
       <c r="P65">
-        <v>43.5074066175</v>
+        <v>43.36179204</v>
       </c>
       <c r="Q65">
-        <v>75.40740661749999</v>
+        <v>75.26179203999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.174585198652967</v>
+        <v>0.1776829613178575</v>
       </c>
       <c r="T65">
-        <v>1.992266064560164</v>
+        <v>2.040187467779436</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.742614150930962</v>
+        <v>5.652885804822666</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08891722607442872</v>
+        <v>0.08867643364725962</v>
       </c>
       <c r="C66">
-        <v>188.698909898176</v>
+        <v>187.1790638744999</v>
       </c>
       <c r="D66">
-        <v>394.438909898176</v>
+        <v>396.6540638744999</v>
       </c>
       <c r="E66">
-        <v>-46.76000000000002</v>
+        <v>-43.02500000000001</v>
       </c>
       <c r="F66">
-        <v>239.04</v>
+        <v>242.775</v>
       </c>
       <c r="G66">
         <v>33.3</v>
@@ -6699,28 +6699,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M66">
-        <v>13.218912</v>
+        <v>13.4254575</v>
       </c>
       <c r="N66">
-        <v>61.50608799999999</v>
+        <v>61.29954249999999</v>
       </c>
       <c r="O66">
-        <v>18.14429596</v>
+        <v>18.0833650375</v>
       </c>
       <c r="P66">
-        <v>43.36179204</v>
+        <v>43.2161774625</v>
       </c>
       <c r="Q66">
-        <v>75.26179203999999</v>
+        <v>75.11617746249999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1776829613178575</v>
+        <v>0.1809577389921703</v>
       </c>
       <c r="T66">
-        <v>2.040187467779436</v>
+        <v>2.090847236896951</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.652885804822666</v>
+        <v>5.565918330902317</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08867643364725962</v>
+        <v>0.08843564122009054</v>
       </c>
       <c r="C67">
-        <v>187.1790638744999</v>
+        <v>185.6842388092166</v>
       </c>
       <c r="D67">
-        <v>396.6540638744999</v>
+        <v>398.8942388092166</v>
       </c>
       <c r="E67">
-        <v>-43.02500000000001</v>
+        <v>-39.28999999999999</v>
       </c>
       <c r="F67">
-        <v>242.775</v>
+        <v>246.51</v>
       </c>
       <c r="G67">
         <v>33.3</v>
@@ -6781,28 +6781,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M67">
-        <v>13.4254575</v>
+        <v>13.632003</v>
       </c>
       <c r="N67">
-        <v>61.29954249999999</v>
+        <v>61.092997</v>
       </c>
       <c r="O67">
-        <v>18.0833650375</v>
+        <v>18.022434115</v>
       </c>
       <c r="P67">
-        <v>43.2161774625</v>
+        <v>43.070562885</v>
       </c>
       <c r="Q67">
-        <v>75.11617746249999</v>
+        <v>74.97056288499999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1809577389921703</v>
+        <v>0.1844251506473251</v>
       </c>
       <c r="T67">
-        <v>2.090847236896951</v>
+        <v>2.144486992433144</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.565918330902317</v>
+        <v>5.481586234979554</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08843564122009054</v>
+        <v>0.08819484879292143</v>
       </c>
       <c r="C68">
-        <v>185.6842388092166</v>
+        <v>184.2148610411959</v>
       </c>
       <c r="D68">
-        <v>398.8942388092166</v>
+        <v>401.1598610411959</v>
       </c>
       <c r="E68">
-        <v>-39.28999999999999</v>
+        <v>-35.55500000000001</v>
       </c>
       <c r="F68">
-        <v>246.51</v>
+        <v>250.245</v>
       </c>
       <c r="G68">
         <v>33.3</v>
@@ -6863,28 +6863,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M68">
-        <v>13.632003</v>
+        <v>13.8385485</v>
       </c>
       <c r="N68">
-        <v>61.092997</v>
+        <v>60.88645149999999</v>
       </c>
       <c r="O68">
-        <v>18.022434115</v>
+        <v>17.9615031925</v>
       </c>
       <c r="P68">
-        <v>43.070562885</v>
+        <v>42.9249483075</v>
       </c>
       <c r="Q68">
-        <v>74.97056288499999</v>
+        <v>74.82494830749999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1844251506473251</v>
+        <v>0.1881027084633983</v>
       </c>
       <c r="T68">
-        <v>2.144486992433144</v>
+        <v>2.201377642244258</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.481586234979554</v>
+        <v>5.399771515054486</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08819484879292143</v>
+        <v>0.08795405636575235</v>
       </c>
       <c r="C69">
-        <v>184.2148610411959</v>
+        <v>182.7713666506395</v>
       </c>
       <c r="D69">
-        <v>401.1598610411959</v>
+        <v>403.4513666506395</v>
       </c>
       <c r="E69">
-        <v>-35.55500000000001</v>
+        <v>-31.81999999999999</v>
       </c>
       <c r="F69">
-        <v>250.245</v>
+        <v>253.98</v>
       </c>
       <c r="G69">
         <v>33.3</v>
@@ -6945,28 +6945,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M69">
-        <v>13.8385485</v>
+        <v>14.045094</v>
       </c>
       <c r="N69">
-        <v>60.88645149999999</v>
+        <v>60.679906</v>
       </c>
       <c r="O69">
-        <v>17.9615031925</v>
+        <v>17.90057227</v>
       </c>
       <c r="P69">
-        <v>42.9249483075</v>
+        <v>42.77933373</v>
       </c>
       <c r="Q69">
-        <v>74.82494830749999</v>
+        <v>74.67933373</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1881027084633983</v>
+        <v>0.1920101136429761</v>
       </c>
       <c r="T69">
-        <v>2.201377642244258</v>
+        <v>2.261823957668566</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.399771515054486</v>
+        <v>5.320363110421332</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08795405636575235</v>
+        <v>0.08771326393858327</v>
       </c>
       <c r="C70">
-        <v>182.7713666506395</v>
+        <v>181.3542017389028</v>
       </c>
       <c r="D70">
-        <v>403.4513666506395</v>
+        <v>405.7692017389028</v>
       </c>
       <c r="E70">
-        <v>-31.81999999999999</v>
+        <v>-28.08499999999998</v>
       </c>
       <c r="F70">
-        <v>253.98</v>
+        <v>257.715</v>
       </c>
       <c r="G70">
         <v>33.3</v>
@@ -7027,28 +7027,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M70">
-        <v>14.045094</v>
+        <v>14.2516395</v>
       </c>
       <c r="N70">
-        <v>60.679906</v>
+        <v>60.47336049999999</v>
       </c>
       <c r="O70">
-        <v>17.90057227</v>
+        <v>17.8396413475</v>
       </c>
       <c r="P70">
-        <v>42.77933373</v>
+        <v>42.63371915249999</v>
       </c>
       <c r="Q70">
-        <v>74.67933373</v>
+        <v>74.5337191525</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1920101136429761</v>
+        <v>0.1961696094793009</v>
       </c>
       <c r="T70">
-        <v>2.261823957668566</v>
+        <v>2.326170035378314</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.320363110421332</v>
+        <v>5.243256398676094</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08771326393858327</v>
+        <v>0.08747247151141417</v>
       </c>
       <c r="C71">
-        <v>181.3542017389028</v>
+        <v>179.9638227180164</v>
       </c>
       <c r="D71">
-        <v>405.7692017389028</v>
+        <v>408.1138227180164</v>
       </c>
       <c r="E71">
-        <v>-28.08499999999998</v>
+        <v>-24.34999999999997</v>
       </c>
       <c r="F71">
-        <v>257.715</v>
+        <v>261.45</v>
       </c>
       <c r="G71">
         <v>33.3</v>
@@ -7109,28 +7109,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M71">
-        <v>14.2516395</v>
+        <v>14.458185</v>
       </c>
       <c r="N71">
-        <v>60.47336049999999</v>
+        <v>60.26681499999999</v>
       </c>
       <c r="O71">
-        <v>17.8396413475</v>
+        <v>17.778710425</v>
       </c>
       <c r="P71">
-        <v>42.63371915249999</v>
+        <v>42.48810457499999</v>
       </c>
       <c r="Q71">
-        <v>74.5337191525</v>
+        <v>74.388104575</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1961696094793009</v>
+        <v>0.2006064050380472</v>
       </c>
       <c r="T71">
-        <v>2.326170035378314</v>
+        <v>2.394805851602044</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.243256398676094</v>
+        <v>5.168352735837865</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08747247151141417</v>
+        <v>0.08723167908424509</v>
       </c>
       <c r="C72">
-        <v>179.9638227180164</v>
+        <v>178.6006966103031</v>
       </c>
       <c r="D72">
-        <v>408.1138227180164</v>
+        <v>410.4856966103031</v>
       </c>
       <c r="E72">
-        <v>-24.34999999999997</v>
+        <v>-20.61500000000001</v>
       </c>
       <c r="F72">
-        <v>261.45</v>
+        <v>265.185</v>
       </c>
       <c r="G72">
         <v>33.3</v>
@@ -7191,28 +7191,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M72">
-        <v>14.458185</v>
+        <v>14.6647305</v>
       </c>
       <c r="N72">
-        <v>60.26681499999999</v>
+        <v>60.06026949999999</v>
       </c>
       <c r="O72">
-        <v>17.778710425</v>
+        <v>17.7177795025</v>
       </c>
       <c r="P72">
-        <v>42.48810457499999</v>
+        <v>42.3424899975</v>
       </c>
       <c r="Q72">
-        <v>74.388104575</v>
+        <v>74.2424899975</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2006064050380472</v>
+        <v>0.2053491864973969</v>
       </c>
       <c r="T72">
-        <v>2.394805851602044</v>
+        <v>2.46817517239293</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.168352735837865</v>
+        <v>5.095559035333107</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08723167908424509</v>
+        <v>0.08699088665707599</v>
       </c>
       <c r="C73">
-        <v>178.6006966103031</v>
+        <v>177.2653013585057</v>
       </c>
       <c r="D73">
-        <v>410.4856966103031</v>
+        <v>412.8853013585057</v>
       </c>
       <c r="E73">
-        <v>-20.61500000000001</v>
+        <v>-16.88</v>
       </c>
       <c r="F73">
-        <v>265.185</v>
+        <v>268.92</v>
       </c>
       <c r="G73">
         <v>33.3</v>
@@ -7273,28 +7273,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M73">
-        <v>14.6647305</v>
+        <v>14.871276</v>
       </c>
       <c r="N73">
-        <v>60.06026949999999</v>
+        <v>59.85372399999999</v>
       </c>
       <c r="O73">
-        <v>17.7177795025</v>
+        <v>17.65684858</v>
       </c>
       <c r="P73">
-        <v>42.3424899975</v>
+        <v>42.19687542</v>
       </c>
       <c r="Q73">
-        <v>74.2424899975</v>
+        <v>74.09687542</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2053491864973968</v>
+        <v>0.2104307380609857</v>
       </c>
       <c r="T73">
-        <v>2.468175172392929</v>
+        <v>2.546785158954591</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.095559035333107</v>
+        <v>5.024787382064591</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08699088665707599</v>
+        <v>0.08675009422990691</v>
       </c>
       <c r="C74">
-        <v>177.2653013585057</v>
+        <v>175.9581261468537</v>
       </c>
       <c r="D74">
-        <v>412.8853013585057</v>
+        <v>415.3131261468537</v>
       </c>
       <c r="E74">
-        <v>-16.88</v>
+        <v>-13.14500000000004</v>
       </c>
       <c r="F74">
-        <v>268.92</v>
+        <v>272.655</v>
       </c>
       <c r="G74">
         <v>33.3</v>
@@ -7355,28 +7355,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M74">
-        <v>14.871276</v>
+        <v>15.0778215</v>
       </c>
       <c r="N74">
-        <v>59.85372399999999</v>
+        <v>59.6471785</v>
       </c>
       <c r="O74">
-        <v>17.65684858</v>
+        <v>17.5959176575</v>
       </c>
       <c r="P74">
-        <v>42.19687542</v>
+        <v>42.0512608425</v>
       </c>
       <c r="Q74">
-        <v>74.09687542</v>
+        <v>73.95126084250001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2104307380609857</v>
+        <v>0.215888700851507</v>
       </c>
       <c r="T74">
-        <v>2.546785158954591</v>
+        <v>2.631218107483783</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.024787382064591</v>
+        <v>4.955954678200694</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08675009422990691</v>
+        <v>0.08650930180273783</v>
       </c>
       <c r="C75">
-        <v>175.9581261468537</v>
+        <v>174.6796717335272</v>
       </c>
       <c r="D75">
-        <v>415.3131261468537</v>
+        <v>417.7696717335272</v>
       </c>
       <c r="E75">
-        <v>-13.14500000000004</v>
+        <v>-9.410000000000025</v>
       </c>
       <c r="F75">
-        <v>272.655</v>
+        <v>276.39</v>
       </c>
       <c r="G75">
         <v>33.3</v>
@@ -7437,28 +7437,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M75">
-        <v>15.0778215</v>
+        <v>15.284367</v>
       </c>
       <c r="N75">
-        <v>59.6471785</v>
+        <v>59.44063299999999</v>
       </c>
       <c r="O75">
-        <v>17.5959176575</v>
+        <v>17.534986735</v>
       </c>
       <c r="P75">
-        <v>42.0512608425</v>
+        <v>41.90564626499999</v>
       </c>
       <c r="Q75">
-        <v>73.95126084250001</v>
+        <v>73.80564626499999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.215888700851507</v>
+        <v>0.221766506933607</v>
       </c>
       <c r="T75">
-        <v>2.631218107483783</v>
+        <v>2.72214589820753</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.955954678200694</v>
+        <v>4.888982317684468</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08650930180273783</v>
+        <v>0.08626850937556874</v>
       </c>
       <c r="C76">
-        <v>174.6796717335272</v>
+        <v>173.4304507949889</v>
       </c>
       <c r="D76">
-        <v>417.7696717335272</v>
+        <v>420.2554507949889</v>
       </c>
       <c r="E76">
-        <v>-9.410000000000025</v>
+        <v>-5.675000000000011</v>
       </c>
       <c r="F76">
-        <v>276.39</v>
+        <v>280.125</v>
       </c>
       <c r="G76">
         <v>33.3</v>
@@ -7519,28 +7519,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M76">
-        <v>15.284367</v>
+        <v>15.4909125</v>
       </c>
       <c r="N76">
-        <v>59.44063299999999</v>
+        <v>59.23408749999999</v>
       </c>
       <c r="O76">
-        <v>17.534986735</v>
+        <v>17.4740558125</v>
       </c>
       <c r="P76">
-        <v>41.90564626499999</v>
+        <v>41.7600316875</v>
       </c>
       <c r="Q76">
-        <v>73.80564626499999</v>
+        <v>73.66003168749999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.221766506933607</v>
+        <v>0.2281145375022749</v>
       </c>
       <c r="T76">
-        <v>2.72214589820753</v>
+        <v>2.820347912189175</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.888982317684468</v>
+        <v>4.823795886782008</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08626850937556874</v>
+        <v>0.08602771694839964</v>
       </c>
       <c r="C77">
-        <v>173.4304507949889</v>
+        <v>172.2109882826811</v>
       </c>
       <c r="D77">
-        <v>420.2554507949889</v>
+        <v>422.7709882826811</v>
       </c>
       <c r="E77">
-        <v>-5.675000000000011</v>
+        <v>-1.939999999999998</v>
       </c>
       <c r="F77">
-        <v>280.125</v>
+        <v>283.86</v>
       </c>
       <c r="G77">
         <v>33.3</v>
@@ -7601,28 +7601,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M77">
-        <v>15.4909125</v>
+        <v>15.697458</v>
       </c>
       <c r="N77">
-        <v>59.23408749999999</v>
+        <v>59.027542</v>
       </c>
       <c r="O77">
-        <v>17.4740558125</v>
+        <v>17.41312489</v>
       </c>
       <c r="P77">
-        <v>41.7600316875</v>
+        <v>41.61441711</v>
       </c>
       <c r="Q77">
-        <v>73.66003168749999</v>
+        <v>73.51441711</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2281145375022749</v>
+        <v>0.2349915706183318</v>
       </c>
       <c r="T77">
-        <v>2.820347912189175</v>
+        <v>2.926733427335958</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.823795886782008</v>
+        <v>4.760324888271718</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08602771694839964</v>
+        <v>0.08578692452123055</v>
       </c>
       <c r="C78">
-        <v>172.2109882826811</v>
+        <v>171.0218217926129</v>
       </c>
       <c r="D78">
-        <v>422.7709882826811</v>
+        <v>425.3168217926129</v>
       </c>
       <c r="E78">
-        <v>-1.939999999999998</v>
+        <v>1.795000000000016</v>
       </c>
       <c r="F78">
-        <v>283.86</v>
+        <v>287.595</v>
       </c>
       <c r="G78">
         <v>33.3</v>
@@ -7683,28 +7683,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M78">
-        <v>15.697458</v>
+        <v>15.9040035</v>
       </c>
       <c r="N78">
-        <v>59.027542</v>
+        <v>58.82099649999999</v>
       </c>
       <c r="O78">
-        <v>17.41312489</v>
+        <v>17.3521939675</v>
       </c>
       <c r="P78">
-        <v>41.61441711</v>
+        <v>41.46880253249999</v>
       </c>
       <c r="Q78">
-        <v>73.51441711</v>
+        <v>73.36880253249998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2349915706183318</v>
+        <v>0.2424666066140458</v>
       </c>
       <c r="T78">
-        <v>2.926733427335958</v>
+        <v>3.04236985684333</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.760324888271718</v>
+        <v>4.698502487125332</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08578692452123055</v>
+        <v>0.08554613209406146</v>
       </c>
       <c r="C79">
-        <v>171.0218217926129</v>
+        <v>169.8635019483804</v>
       </c>
       <c r="D79">
-        <v>425.3168217926129</v>
+        <v>427.8935019483804</v>
       </c>
       <c r="E79">
-        <v>1.795000000000016</v>
+        <v>5.529999999999973</v>
       </c>
       <c r="F79">
-        <v>287.595</v>
+        <v>291.33</v>
       </c>
       <c r="G79">
         <v>33.3</v>
@@ -7765,28 +7765,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M79">
-        <v>15.9040035</v>
+        <v>16.110549</v>
       </c>
       <c r="N79">
-        <v>58.82099649999999</v>
+        <v>58.614451</v>
       </c>
       <c r="O79">
-        <v>17.3521939675</v>
+        <v>17.291263045</v>
       </c>
       <c r="P79">
-        <v>41.46880253249999</v>
+        <v>41.32318795499999</v>
       </c>
       <c r="Q79">
-        <v>73.36880253249998</v>
+        <v>73.22318795499999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2424666066140458</v>
+        <v>0.250621191336643</v>
       </c>
       <c r="T79">
-        <v>3.04236985684333</v>
+        <v>3.168518689033191</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.698502487125332</v>
+        <v>4.638265275751931</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08554613209406146</v>
+        <v>0.08530533966689237</v>
       </c>
       <c r="C80">
-        <v>169.8635019483804</v>
+        <v>168.7365927981949</v>
       </c>
       <c r="D80">
-        <v>427.8935019483804</v>
+        <v>430.5015927981948</v>
       </c>
       <c r="E80">
-        <v>5.529999999999973</v>
+        <v>9.264999999999986</v>
       </c>
       <c r="F80">
-        <v>291.33</v>
+        <v>295.065</v>
       </c>
       <c r="G80">
         <v>33.3</v>
@@ -7847,28 +7847,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M80">
-        <v>16.110549</v>
+        <v>16.3170945</v>
       </c>
       <c r="N80">
-        <v>58.614451</v>
+        <v>58.4079055</v>
       </c>
       <c r="O80">
-        <v>17.291263045</v>
+        <v>17.2303321225</v>
       </c>
       <c r="P80">
-        <v>41.32318795499999</v>
+        <v>41.1775733775</v>
       </c>
       <c r="Q80">
-        <v>73.22318795499999</v>
+        <v>73.07757337749999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.250621191336643</v>
+        <v>0.259552403175678</v>
       </c>
       <c r="T80">
-        <v>3.168518689033191</v>
+        <v>3.306681695717325</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.638265275751931</v>
+        <v>4.579553057071527</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08530533966689237</v>
+        <v>0.08506454723972329</v>
       </c>
       <c r="C81">
-        <v>168.7365927981949</v>
+        <v>167.6416722265184</v>
       </c>
       <c r="D81">
-        <v>430.5015927981948</v>
+        <v>433.1416722265184</v>
       </c>
       <c r="E81">
-        <v>9.264999999999986</v>
+        <v>13</v>
       </c>
       <c r="F81">
-        <v>295.065</v>
+        <v>298.8</v>
       </c>
       <c r="G81">
         <v>33.3</v>
@@ -7929,28 +7929,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M81">
-        <v>16.3170945</v>
+        <v>16.52364</v>
       </c>
       <c r="N81">
-        <v>58.4079055</v>
+        <v>58.20135999999999</v>
       </c>
       <c r="O81">
-        <v>17.2303321225</v>
+        <v>17.1694012</v>
       </c>
       <c r="P81">
-        <v>41.1775733775</v>
+        <v>41.0319588</v>
       </c>
       <c r="Q81">
-        <v>73.07757337749999</v>
+        <v>72.93195879999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.259552403175678</v>
+        <v>0.2693767361986165</v>
       </c>
       <c r="T81">
-        <v>3.306681695717325</v>
+        <v>3.458661003069872</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.579553057071527</v>
+        <v>4.522308643858132</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08506454723972329</v>
+        <v>0.08625137981255418</v>
       </c>
       <c r="C82">
-        <v>167.6416722265184</v>
+        <v>151.1984123938259</v>
       </c>
       <c r="D82">
-        <v>433.1416722265184</v>
+        <v>420.4334123938259</v>
       </c>
       <c r="E82">
-        <v>13</v>
+        <v>16.73500000000001</v>
       </c>
       <c r="F82">
-        <v>298.8</v>
+        <v>302.535</v>
       </c>
       <c r="G82">
         <v>33.3</v>
@@ -8011,45 +8011,45 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M82">
-        <v>16.52364</v>
+        <v>17.486523</v>
       </c>
       <c r="N82">
-        <v>58.20135999999999</v>
+        <v>57.23847699999999</v>
       </c>
       <c r="O82">
-        <v>17.1694012</v>
+        <v>16.88535071499999</v>
       </c>
       <c r="P82">
-        <v>41.0319588</v>
+        <v>40.35312628499999</v>
       </c>
       <c r="Q82">
-        <v>72.93195879999999</v>
+        <v>72.25312628499999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2693767361986165</v>
+        <v>0.2802352095397589</v>
       </c>
       <c r="T82">
-        <v>3.458661003069872</v>
+        <v>3.626638132249002</v>
       </c>
       <c r="U82">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V82">
         <v>0.295</v>
       </c>
       <c r="W82">
-        <v>0.03898650000000001</v>
+        <v>0.04074900000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>4.522308643858132</v>
+        <v>4.273290922386342</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08625137981255418</v>
+        <v>0.08602821238538511</v>
       </c>
       <c r="C83">
-        <v>151.1984123938259</v>
+        <v>149.7957815789386</v>
       </c>
       <c r="D83">
-        <v>420.4334123938259</v>
+        <v>422.7657815789386</v>
       </c>
       <c r="E83">
-        <v>16.73500000000001</v>
+        <v>20.47000000000003</v>
       </c>
       <c r="F83">
-        <v>302.535</v>
+        <v>306.27</v>
       </c>
       <c r="G83">
         <v>33.3</v>
@@ -8093,28 +8093,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M83">
-        <v>17.486523</v>
+        <v>17.702406</v>
       </c>
       <c r="N83">
-        <v>57.23847699999999</v>
+        <v>57.02259399999999</v>
       </c>
       <c r="O83">
-        <v>16.88535071499999</v>
+        <v>16.82166523</v>
       </c>
       <c r="P83">
-        <v>40.35312628499999</v>
+        <v>40.20092876999999</v>
       </c>
       <c r="Q83">
-        <v>72.25312628499999</v>
+        <v>72.10092877</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2802352095397589</v>
+        <v>0.2923001799188062</v>
       </c>
       <c r="T83">
-        <v>3.626638132249002</v>
+        <v>3.813279386892481</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.273290922386342</v>
+        <v>4.221177618454801</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08602821238538511</v>
+        <v>0.08580504495821603</v>
       </c>
       <c r="C84">
-        <v>149.7957815789386</v>
+        <v>148.4191729235462</v>
       </c>
       <c r="D84">
-        <v>422.7657815789386</v>
+        <v>425.1241729235463</v>
       </c>
       <c r="E84">
-        <v>20.47000000000003</v>
+        <v>24.20500000000004</v>
       </c>
       <c r="F84">
-        <v>306.27</v>
+        <v>310.0050000000001</v>
       </c>
       <c r="G84">
         <v>33.3</v>
@@ -8175,28 +8175,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M84">
-        <v>17.702406</v>
+        <v>17.91828900000001</v>
       </c>
       <c r="N84">
-        <v>57.02259399999999</v>
+        <v>56.80671099999999</v>
       </c>
       <c r="O84">
-        <v>16.82166523</v>
+        <v>16.757979745</v>
       </c>
       <c r="P84">
-        <v>40.20092876999999</v>
+        <v>40.04873125499999</v>
       </c>
       <c r="Q84">
-        <v>72.10092877</v>
+        <v>71.94873125499998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2923001799188062</v>
+        <v>0.3057845585777414</v>
       </c>
       <c r="T84">
-        <v>3.813279386892481</v>
+        <v>4.021878436199898</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.221177618454801</v>
+        <v>4.170320056786671</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08580504495821603</v>
+        <v>0.08558187753104693</v>
       </c>
       <c r="C85">
-        <v>148.4191729235462</v>
+        <v>147.0690243631169</v>
       </c>
       <c r="D85">
-        <v>425.1241729235463</v>
+        <v>427.5090243631169</v>
       </c>
       <c r="E85">
-        <v>24.20500000000004</v>
+        <v>27.94</v>
       </c>
       <c r="F85">
-        <v>310.0050000000001</v>
+        <v>313.74</v>
       </c>
       <c r="G85">
         <v>33.3</v>
@@ -8257,28 +8257,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M85">
-        <v>17.91828900000001</v>
+        <v>18.134172</v>
       </c>
       <c r="N85">
-        <v>56.80671099999999</v>
+        <v>56.59082799999999</v>
       </c>
       <c r="O85">
-        <v>16.757979745</v>
+        <v>16.69429426</v>
       </c>
       <c r="P85">
-        <v>40.04873125499999</v>
+        <v>39.89653374</v>
       </c>
       <c r="Q85">
-        <v>71.94873125499998</v>
+        <v>71.79653374</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3057845585777414</v>
+        <v>0.3209544845690435</v>
       </c>
       <c r="T85">
-        <v>4.021878436199898</v>
+        <v>4.256552366670744</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.170320056786671</v>
+        <v>4.120673389443972</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08558187753104693</v>
+        <v>0.08535871010387786</v>
       </c>
       <c r="C86">
-        <v>147.0690243631169</v>
+        <v>145.7457837154353</v>
       </c>
       <c r="D86">
-        <v>427.5090243631169</v>
+        <v>429.9207837154352</v>
       </c>
       <c r="E86">
-        <v>27.94</v>
+        <v>31.67499999999995</v>
       </c>
       <c r="F86">
-        <v>313.74</v>
+        <v>317.475</v>
       </c>
       <c r="G86">
         <v>33.3</v>
@@ -8339,28 +8339,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M86">
-        <v>18.134172</v>
+        <v>18.350055</v>
       </c>
       <c r="N86">
-        <v>56.59082799999999</v>
+        <v>56.374945</v>
       </c>
       <c r="O86">
-        <v>16.69429426</v>
+        <v>16.630608775</v>
       </c>
       <c r="P86">
-        <v>39.89653374</v>
+        <v>39.744336225</v>
       </c>
       <c r="Q86">
-        <v>71.79653374</v>
+        <v>71.64433622499999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3209544845690433</v>
+        <v>0.3381470673591856</v>
       </c>
       <c r="T86">
-        <v>4.256552366670741</v>
+        <v>4.522516154537698</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.120673389443972</v>
+        <v>4.072194878979927</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08535871010387786</v>
+        <v>0.08513554267670875</v>
       </c>
       <c r="C87">
-        <v>145.7457837154353</v>
+        <v>144.4499089609377</v>
       </c>
       <c r="D87">
-        <v>429.9207837154352</v>
+        <v>432.3599089609377</v>
       </c>
       <c r="E87">
-        <v>31.67499999999995</v>
+        <v>35.40999999999997</v>
       </c>
       <c r="F87">
-        <v>317.475</v>
+        <v>321.21</v>
       </c>
       <c r="G87">
         <v>33.3</v>
@@ -8421,28 +8421,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M87">
-        <v>18.350055</v>
+        <v>18.565938</v>
       </c>
       <c r="N87">
-        <v>56.374945</v>
+        <v>56.15906199999999</v>
       </c>
       <c r="O87">
-        <v>16.630608775</v>
+        <v>16.56692329</v>
       </c>
       <c r="P87">
-        <v>39.744336225</v>
+        <v>39.59213870999999</v>
       </c>
       <c r="Q87">
-        <v>71.64433622499999</v>
+        <v>71.49213870999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3381470673591856</v>
+        <v>0.3577957334050625</v>
       </c>
       <c r="T87">
-        <v>4.522516154537698</v>
+        <v>4.826474769242791</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.072194878979927</v>
+        <v>4.024843775735974</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08513554267670875</v>
+        <v>0.08705910024953967</v>
       </c>
       <c r="C88">
-        <v>144.4499089609377</v>
+        <v>120.5576788701148</v>
       </c>
       <c r="D88">
-        <v>432.3599089609377</v>
+        <v>412.2026788701148</v>
       </c>
       <c r="E88">
-        <v>35.40999999999997</v>
+        <v>39.14499999999998</v>
       </c>
       <c r="F88">
-        <v>321.21</v>
+        <v>324.945</v>
       </c>
       <c r="G88">
         <v>33.3</v>
@@ -8503,45 +8503,45 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M88">
-        <v>18.565938</v>
+        <v>19.9191285</v>
       </c>
       <c r="N88">
-        <v>56.15906199999999</v>
+        <v>54.80587149999999</v>
       </c>
       <c r="O88">
-        <v>16.56692329</v>
+        <v>16.1677320925</v>
       </c>
       <c r="P88">
-        <v>39.59213870999999</v>
+        <v>38.6381394075</v>
       </c>
       <c r="Q88">
-        <v>71.49213870999999</v>
+        <v>70.5381394075</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3577957334050625</v>
+        <v>0.3804672711503051</v>
       </c>
       <c r="T88">
-        <v>4.826474769242791</v>
+        <v>5.177196247748668</v>
       </c>
       <c r="U88">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V88">
         <v>0.295</v>
       </c>
       <c r="W88">
-        <v>0.04074900000000001</v>
+        <v>0.0432165</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>4.024843775735974</v>
+        <v>3.7514191446679</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08705910024953967</v>
+        <v>0.08686060782237058</v>
       </c>
       <c r="C89">
-        <v>120.5576788701148</v>
+        <v>118.8153213212076</v>
       </c>
       <c r="D89">
-        <v>412.2026788701148</v>
+        <v>414.1953213212076</v>
       </c>
       <c r="E89">
-        <v>39.14499999999998</v>
+        <v>42.88</v>
       </c>
       <c r="F89">
-        <v>324.945</v>
+        <v>328.68</v>
       </c>
       <c r="G89">
         <v>33.3</v>
@@ -8585,28 +8585,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M89">
-        <v>19.9191285</v>
+        <v>20.148084</v>
       </c>
       <c r="N89">
-        <v>54.80587149999999</v>
+        <v>54.576916</v>
       </c>
       <c r="O89">
-        <v>16.1677320925</v>
+        <v>16.10019022</v>
       </c>
       <c r="P89">
-        <v>38.6381394075</v>
+        <v>38.47672578</v>
       </c>
       <c r="Q89">
-        <v>70.5381394075</v>
+        <v>70.37672577999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3804672711503051</v>
+        <v>0.4069173985197548</v>
       </c>
       <c r="T89">
-        <v>5.177196247748668</v>
+        <v>5.586371306005526</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.7514191446679</v>
+        <v>3.70878938166031</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08686060782237058</v>
+        <v>0.08666211539520149</v>
       </c>
       <c r="C90">
-        <v>118.8153213212076</v>
+        <v>117.0923227522637</v>
       </c>
       <c r="D90">
-        <v>414.1953213212076</v>
+        <v>416.2073227522637</v>
       </c>
       <c r="E90">
-        <v>42.88</v>
+        <v>46.61500000000001</v>
       </c>
       <c r="F90">
-        <v>328.68</v>
+        <v>332.415</v>
       </c>
       <c r="G90">
         <v>33.3</v>
@@ -8667,28 +8667,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M90">
-        <v>20.148084</v>
+        <v>20.3770395</v>
       </c>
       <c r="N90">
-        <v>54.576916</v>
+        <v>54.34796049999999</v>
       </c>
       <c r="O90">
-        <v>16.10019022</v>
+        <v>16.0326483475</v>
       </c>
       <c r="P90">
-        <v>38.47672578</v>
+        <v>38.3153121525</v>
       </c>
       <c r="Q90">
-        <v>70.37672577999999</v>
+        <v>70.21531215249999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4069173985197548</v>
+        <v>0.4381766399563772</v>
       </c>
       <c r="T90">
-        <v>5.586371306005526</v>
+        <v>6.069941829399992</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.70878938166031</v>
+        <v>3.667117590855138</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08666211539520149</v>
+        <v>0.08646362296803239</v>
       </c>
       <c r="C91">
-        <v>117.0923227522637</v>
+        <v>115.3889666557988</v>
       </c>
       <c r="D91">
-        <v>416.2073227522637</v>
+        <v>418.2389666557988</v>
       </c>
       <c r="E91">
-        <v>46.61500000000001</v>
+        <v>50.35000000000002</v>
       </c>
       <c r="F91">
-        <v>332.415</v>
+        <v>336.15</v>
       </c>
       <c r="G91">
         <v>33.3</v>
@@ -8749,28 +8749,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M91">
-        <v>20.3770395</v>
+        <v>20.605995</v>
       </c>
       <c r="N91">
-        <v>54.34796049999999</v>
+        <v>54.11900499999999</v>
       </c>
       <c r="O91">
-        <v>16.0326483475</v>
+        <v>15.965106475</v>
       </c>
       <c r="P91">
-        <v>38.3153121525</v>
+        <v>38.15389852499999</v>
       </c>
       <c r="Q91">
-        <v>70.21531215249999</v>
+        <v>70.05389852499999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4381766399563772</v>
+        <v>0.475687729680324</v>
       </c>
       <c r="T91">
-        <v>6.069941829399992</v>
+        <v>6.650226457473353</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.667117590855138</v>
+        <v>3.626371839845636</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08646362296803239</v>
+        <v>0.08626513054086332</v>
       </c>
       <c r="C92">
-        <v>115.3889666557988</v>
+        <v>113.705542086758</v>
       </c>
       <c r="D92">
-        <v>418.2389666557988</v>
+        <v>420.290542086758</v>
       </c>
       <c r="E92">
-        <v>50.35000000000002</v>
+        <v>54.08499999999998</v>
       </c>
       <c r="F92">
-        <v>336.15</v>
+        <v>339.885</v>
       </c>
       <c r="G92">
         <v>33.3</v>
@@ -8831,28 +8831,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M92">
-        <v>20.605995</v>
+        <v>20.8349505</v>
       </c>
       <c r="N92">
-        <v>54.11900499999999</v>
+        <v>53.8900495</v>
       </c>
       <c r="O92">
-        <v>15.965106475</v>
+        <v>15.8975646025</v>
       </c>
       <c r="P92">
-        <v>38.15389852499999</v>
+        <v>37.9924848975</v>
       </c>
       <c r="Q92">
-        <v>70.05389852499999</v>
+        <v>69.8924848975</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.475687729680324</v>
+        <v>0.5215346171207036</v>
       </c>
       <c r="T92">
-        <v>6.650226457473353</v>
+        <v>7.359463225118573</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.626371839845636</v>
+        <v>3.586521599847333</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08626513054086332</v>
+        <v>0.08606663811369422</v>
       </c>
       <c r="C93">
-        <v>113.705542086758</v>
+        <v>112.0423437996168</v>
       </c>
       <c r="D93">
-        <v>420.290542086758</v>
+        <v>422.3623437996168</v>
       </c>
       <c r="E93">
-        <v>54.08499999999998</v>
+        <v>57.81999999999999</v>
       </c>
       <c r="F93">
-        <v>339.885</v>
+        <v>343.62</v>
       </c>
       <c r="G93">
         <v>33.3</v>
@@ -8913,28 +8913,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M93">
-        <v>20.8349505</v>
+        <v>21.063906</v>
       </c>
       <c r="N93">
-        <v>53.8900495</v>
+        <v>53.66109399999999</v>
       </c>
       <c r="O93">
-        <v>15.8975646025</v>
+        <v>15.83002273</v>
       </c>
       <c r="P93">
-        <v>37.9924848975</v>
+        <v>37.83107127</v>
       </c>
       <c r="Q93">
-        <v>69.8924848975</v>
+        <v>69.73107127</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5215346171207036</v>
+        <v>0.5788432264211779</v>
       </c>
       <c r="T93">
-        <v>7.359463225118573</v>
+        <v>8.246009184675096</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.586521599847333</v>
+        <v>3.54753766941421</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08606663811369422</v>
+        <v>0.08586814568652514</v>
       </c>
       <c r="C94">
-        <v>112.0423437996168</v>
+        <v>110.3996723895522</v>
       </c>
       <c r="D94">
-        <v>422.3623437996168</v>
+        <v>424.4546723895522</v>
       </c>
       <c r="E94">
-        <v>57.81999999999999</v>
+        <v>61.55500000000001</v>
       </c>
       <c r="F94">
-        <v>343.62</v>
+        <v>347.355</v>
       </c>
       <c r="G94">
         <v>33.3</v>
@@ -8995,28 +8995,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M94">
-        <v>21.063906</v>
+        <v>21.2928615</v>
       </c>
       <c r="N94">
-        <v>53.66109399999999</v>
+        <v>53.43213849999999</v>
       </c>
       <c r="O94">
-        <v>15.83002273</v>
+        <v>15.7624808575</v>
       </c>
       <c r="P94">
-        <v>37.83107127</v>
+        <v>37.6696576425</v>
       </c>
       <c r="Q94">
-        <v>69.73107127</v>
+        <v>69.5696576425</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5788432264211779</v>
+        <v>0.6525257240932166</v>
       </c>
       <c r="T94">
-        <v>8.246009184675096</v>
+        <v>9.3858539898192</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.54753766941421</v>
+        <v>3.509392103076423</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08586814568652514</v>
+        <v>0.08752521325935604</v>
       </c>
       <c r="C95">
-        <v>110.3996723895522</v>
+        <v>89.80795629845869</v>
       </c>
       <c r="D95">
-        <v>424.4546723895522</v>
+        <v>407.5979562984587</v>
       </c>
       <c r="E95">
-        <v>61.55500000000001</v>
+        <v>65.29000000000002</v>
       </c>
       <c r="F95">
-        <v>347.355</v>
+        <v>351.09</v>
       </c>
       <c r="G95">
         <v>33.3</v>
@@ -9077,45 +9077,45 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M95">
-        <v>21.2928615</v>
+        <v>22.504869</v>
       </c>
       <c r="N95">
-        <v>53.43213849999999</v>
+        <v>52.22013099999999</v>
       </c>
       <c r="O95">
-        <v>15.7624808575</v>
+        <v>15.404938645</v>
       </c>
       <c r="P95">
-        <v>37.6696576425</v>
+        <v>36.81519235499999</v>
       </c>
       <c r="Q95">
-        <v>69.5696576425</v>
+        <v>68.715192355</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6525257240932166</v>
+        <v>0.7507690543226013</v>
       </c>
       <c r="T95">
-        <v>9.3858539898192</v>
+        <v>10.90564706334467</v>
       </c>
       <c r="U95">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V95">
         <v>0.295</v>
       </c>
       <c r="W95">
-        <v>0.0432165</v>
+        <v>0.04519050000000001</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y95">
-        <v>3.509392103076423</v>
+        <v>3.320392578157197</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08752521325935604</v>
+        <v>0.08734646083218697</v>
       </c>
       <c r="C96">
-        <v>89.80795629845869</v>
+        <v>87.82663453092692</v>
       </c>
       <c r="D96">
-        <v>407.5979562984587</v>
+        <v>409.351634530927</v>
       </c>
       <c r="E96">
-        <v>65.29000000000002</v>
+        <v>69.02500000000003</v>
       </c>
       <c r="F96">
-        <v>351.09</v>
+        <v>354.825</v>
       </c>
       <c r="G96">
         <v>33.3</v>
@@ -9159,28 +9159,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M96">
-        <v>22.504869</v>
+        <v>22.7442825</v>
       </c>
       <c r="N96">
-        <v>52.22013099999999</v>
+        <v>51.98071749999999</v>
       </c>
       <c r="O96">
-        <v>15.404938645</v>
+        <v>15.3343116625</v>
       </c>
       <c r="P96">
-        <v>36.81519235499999</v>
+        <v>36.6464058375</v>
       </c>
       <c r="Q96">
-        <v>68.715192355</v>
+        <v>68.5464058375</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7507690543226013</v>
+        <v>0.8883097166437403</v>
       </c>
       <c r="T96">
-        <v>10.90564706334467</v>
+        <v>13.03335736628033</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.320392578157197</v>
+        <v>3.28544107733449</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08734646083218697</v>
+        <v>0.08716770840501788</v>
       </c>
       <c r="C97">
-        <v>87.82663453092692</v>
+        <v>85.86046826765778</v>
       </c>
       <c r="D97">
-        <v>409.351634530927</v>
+        <v>411.1204682676578</v>
       </c>
       <c r="E97">
-        <v>69.02500000000003</v>
+        <v>72.75999999999999</v>
       </c>
       <c r="F97">
-        <v>354.825</v>
+        <v>358.56</v>
       </c>
       <c r="G97">
         <v>33.3</v>
@@ -9241,28 +9241,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M97">
-        <v>22.7442825</v>
+        <v>22.983696</v>
       </c>
       <c r="N97">
-        <v>51.98071749999999</v>
+        <v>51.74130399999999</v>
       </c>
       <c r="O97">
-        <v>15.3343116625</v>
+        <v>15.26368468</v>
       </c>
       <c r="P97">
-        <v>36.6464058375</v>
+        <v>36.47761932</v>
       </c>
       <c r="Q97">
-        <v>68.5464058375</v>
+        <v>68.37761931999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8883097166437403</v>
+        <v>1.094620710125449</v>
       </c>
       <c r="T97">
-        <v>13.03335736628033</v>
+        <v>16.22492282068382</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.28544107733449</v>
+        <v>3.251217732778922</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08716770840501789</v>
+        <v>0.08698895597784879</v>
       </c>
       <c r="C98">
-        <v>85.86046826765767</v>
+        <v>83.90965482488099</v>
       </c>
       <c r="D98">
-        <v>411.1204682676577</v>
+        <v>412.904654824881</v>
       </c>
       <c r="E98">
-        <v>72.75999999999999</v>
+        <v>76.495</v>
       </c>
       <c r="F98">
-        <v>358.56</v>
+        <v>362.295</v>
       </c>
       <c r="G98">
         <v>33.3</v>
@@ -9323,28 +9323,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M98">
-        <v>22.983696</v>
+        <v>23.2231095</v>
       </c>
       <c r="N98">
-        <v>51.74130399999999</v>
+        <v>51.50189049999999</v>
       </c>
       <c r="O98">
-        <v>15.26368468</v>
+        <v>15.1930576975</v>
       </c>
       <c r="P98">
-        <v>36.47761932</v>
+        <v>36.30883280249999</v>
       </c>
       <c r="Q98">
-        <v>68.37761931999999</v>
+        <v>68.20883280249998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.094620710125446</v>
+        <v>1.438472365928292</v>
       </c>
       <c r="T98">
-        <v>16.22492282068378</v>
+        <v>21.54419857802291</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.251217732778922</v>
+        <v>3.217700024193572</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08698895597784879</v>
+        <v>0.0868102035506797</v>
       </c>
       <c r="C99">
-        <v>83.90965482488099</v>
+        <v>81.97439495901989</v>
       </c>
       <c r="D99">
-        <v>412.904654824881</v>
+        <v>414.7043949590199</v>
       </c>
       <c r="E99">
-        <v>76.495</v>
+        <v>80.22999999999996</v>
       </c>
       <c r="F99">
-        <v>362.295</v>
+        <v>366.03</v>
       </c>
       <c r="G99">
         <v>33.3</v>
@@ -9405,28 +9405,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M99">
-        <v>23.2231095</v>
+        <v>23.462523</v>
       </c>
       <c r="N99">
-        <v>51.50189049999999</v>
+        <v>51.26247699999999</v>
       </c>
       <c r="O99">
-        <v>15.1930576975</v>
+        <v>15.122430715</v>
       </c>
       <c r="P99">
-        <v>36.30883280249999</v>
+        <v>36.140046285</v>
       </c>
       <c r="Q99">
-        <v>68.20883280249998</v>
+        <v>68.04004628499999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.438472365928292</v>
+        <v>2.126175677533983</v>
       </c>
       <c r="T99">
-        <v>21.54419857802291</v>
+        <v>32.18275009270117</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.217700024193572</v>
+        <v>3.184866350477312</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0868102035506797</v>
+        <v>0.08663145112351062</v>
       </c>
       <c r="C100">
-        <v>81.97439495901989</v>
+        <v>80.05489294199333</v>
       </c>
       <c r="D100">
-        <v>414.7043949590199</v>
+        <v>416.5198929419933</v>
       </c>
       <c r="E100">
-        <v>80.22999999999996</v>
+        <v>83.96499999999997</v>
       </c>
       <c r="F100">
-        <v>366.03</v>
+        <v>369.765</v>
       </c>
       <c r="G100">
         <v>33.3</v>
@@ -9487,28 +9487,28 @@
         <v>74.72499999999999</v>
       </c>
       <c r="M100">
-        <v>23.462523</v>
+        <v>23.7019365</v>
       </c>
       <c r="N100">
-        <v>51.26247699999999</v>
+        <v>51.02306349999999</v>
       </c>
       <c r="O100">
-        <v>15.122430715</v>
+        <v>15.0518037325</v>
       </c>
       <c r="P100">
-        <v>36.140046285</v>
+        <v>35.97125976749999</v>
       </c>
       <c r="Q100">
-        <v>68.04004628499999</v>
+        <v>67.87125976749999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.126175677533983</v>
+        <v>4.189285612351057</v>
       </c>
       <c r="T100">
-        <v>32.18275009270117</v>
+        <v>64.09840463673595</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.184866350477312</v>
+        <v>3.152695983300773</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08663145112351062</v>
-      </c>
-      <c r="C101">
-        <v>80.05489294199333</v>
-      </c>
-      <c r="D101">
-        <v>416.5198929419933</v>
-      </c>
-      <c r="E101">
-        <v>83.96499999999997</v>
-      </c>
-      <c r="F101">
-        <v>369.765</v>
-      </c>
-      <c r="G101">
-        <v>33.3</v>
-      </c>
-      <c r="H101">
-        <v>87.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>106.625</v>
-      </c>
-      <c r="K101">
-        <v>31.9</v>
-      </c>
-      <c r="L101">
-        <v>74.72499999999999</v>
-      </c>
-      <c r="M101">
-        <v>23.7019365</v>
-      </c>
-      <c r="N101">
-        <v>51.02306349999999</v>
-      </c>
-      <c r="O101">
-        <v>15.0518037325</v>
-      </c>
-      <c r="P101">
-        <v>35.97125976749999</v>
-      </c>
-      <c r="Q101">
-        <v>67.87125976749999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.189285612351057</v>
-      </c>
-      <c r="T101">
-        <v>64.09840463673595</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.295</v>
-      </c>
-      <c r="W101">
-        <v>0.04519050000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.152695983300773</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
